--- a/research/traditional_assets/database/data/tanzania/tanzania_tobacco.xlsx
+++ b/research/traditional_assets/database/data/tanzania/tanzania_tobacco.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1034249609558353</v>
+        <v>0.1031461860729678</v>
       </c>
       <c r="C2">
-        <v>707.2812462055296</v>
+        <v>703.5408407091921</v>
       </c>
       <c r="D2">
-        <v>685.4812462055296</v>
+        <v>688.8135507091922</v>
       </c>
       <c r="E2">
-        <v>-0.07099999999999999</v>
+        <v>7.001710000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.072710000000001</v>
       </c>
       <c r="G2">
         <v>21.8</v>
@@ -1451,28 +1451,28 @@
         <v>60.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.355757313</v>
       </c>
       <c r="N2">
-        <v>60.6</v>
+        <v>60.244242687</v>
       </c>
       <c r="O2">
-        <v>18.18</v>
+        <v>18.0732728061</v>
       </c>
       <c r="P2">
-        <v>42.42</v>
+        <v>42.1709698809</v>
       </c>
       <c r="Q2">
-        <v>45.72</v>
+        <v>45.4709698809</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1034249609558353</v>
+        <v>0.103832410174715</v>
       </c>
       <c r="T2">
-        <v>0.5572774141861078</v>
+        <v>0.5612177595389388</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>170.3408413139212</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1031461860729678</v>
+        <v>0.1028674111901003</v>
       </c>
       <c r="C3">
-        <v>703.5408407091921</v>
+        <v>699.8329918954976</v>
       </c>
       <c r="D3">
-        <v>688.8135507091922</v>
+        <v>692.1784118954976</v>
       </c>
       <c r="E3">
-        <v>7.001710000000001</v>
+        <v>14.07442</v>
       </c>
       <c r="F3">
-        <v>7.072710000000001</v>
+        <v>14.14542</v>
       </c>
       <c r="G3">
         <v>21.8</v>
@@ -1533,28 +1533,28 @@
         <v>60.6</v>
       </c>
       <c r="M3">
-        <v>0.355757313</v>
+        <v>0.711514626</v>
       </c>
       <c r="N3">
-        <v>60.244242687</v>
+        <v>59.888485374</v>
       </c>
       <c r="O3">
-        <v>18.0732728061</v>
+        <v>17.9665456122</v>
       </c>
       <c r="P3">
-        <v>42.1709698809</v>
+        <v>41.9219397618</v>
       </c>
       <c r="Q3">
-        <v>45.4709698809</v>
+        <v>45.2219397618</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.103832410174715</v>
+        <v>0.1042481746837758</v>
       </c>
       <c r="T3">
-        <v>0.5612177595389388</v>
+        <v>0.5652385201030521</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>170.3408413139212</v>
+        <v>85.1704206569606</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1028674111901003</v>
+        <v>0.1025886363072328</v>
       </c>
       <c r="C4">
-        <v>699.8329918954976</v>
+        <v>696.1581792257953</v>
       </c>
       <c r="D4">
-        <v>692.1784118954976</v>
+        <v>695.5763092257953</v>
       </c>
       <c r="E4">
-        <v>14.07442</v>
+        <v>21.14713</v>
       </c>
       <c r="F4">
-        <v>14.14542</v>
+        <v>21.21813</v>
       </c>
       <c r="G4">
         <v>21.8</v>
@@ -1615,28 +1615,28 @@
         <v>60.6</v>
       </c>
       <c r="M4">
-        <v>0.711514626</v>
+        <v>1.067271939</v>
       </c>
       <c r="N4">
-        <v>59.888485374</v>
+        <v>59.532728061</v>
       </c>
       <c r="O4">
-        <v>17.9665456122</v>
+        <v>17.8598184183</v>
       </c>
       <c r="P4">
-        <v>41.9219397618</v>
+        <v>41.67290964270001</v>
       </c>
       <c r="Q4">
-        <v>45.2219397618</v>
+        <v>44.9729096427</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1042481746837758</v>
+        <v>0.104672511656941</v>
       </c>
       <c r="T4">
-        <v>0.5652385201030521</v>
+        <v>0.5693421829468379</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>85.1704206569606</v>
+        <v>56.78028043797374</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1025886363072328</v>
+        <v>0.1023098614243653</v>
       </c>
       <c r="C5">
-        <v>696.1581792257953</v>
+        <v>692.5168916225633</v>
       </c>
       <c r="D5">
-        <v>695.5763092257953</v>
+        <v>699.0077316225634</v>
       </c>
       <c r="E5">
-        <v>21.14713</v>
+        <v>28.21984</v>
       </c>
       <c r="F5">
-        <v>21.21813</v>
+        <v>28.29084</v>
       </c>
       <c r="G5">
         <v>21.8</v>
@@ -1697,28 +1697,28 @@
         <v>60.6</v>
       </c>
       <c r="M5">
-        <v>1.067271939</v>
+        <v>1.423029252</v>
       </c>
       <c r="N5">
-        <v>59.532728061</v>
+        <v>59.176970748</v>
       </c>
       <c r="O5">
-        <v>17.8598184183</v>
+        <v>17.7530912244</v>
       </c>
       <c r="P5">
-        <v>41.67290964270001</v>
+        <v>41.42387952360001</v>
       </c>
       <c r="Q5">
-        <v>44.9729096427</v>
+        <v>44.7238795236</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.104672511656941</v>
+        <v>0.1051056889837138</v>
       </c>
       <c r="T5">
-        <v>0.5693421829468379</v>
+        <v>0.5735313387665358</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>56.78028043797374</v>
+        <v>42.5852103284803</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1023098614243653</v>
+        <v>0.1020310865414978</v>
       </c>
       <c r="C6">
-        <v>692.5168916225633</v>
+        <v>688.9096277039361</v>
       </c>
       <c r="D6">
-        <v>699.0077316225634</v>
+        <v>702.4731777039361</v>
       </c>
       <c r="E6">
-        <v>28.21984</v>
+        <v>35.29255000000001</v>
       </c>
       <c r="F6">
-        <v>28.29084</v>
+        <v>35.36355</v>
       </c>
       <c r="G6">
         <v>21.8</v>
@@ -1779,28 +1779,28 @@
         <v>60.6</v>
       </c>
       <c r="M6">
-        <v>1.423029252</v>
+        <v>1.778786565</v>
       </c>
       <c r="N6">
-        <v>59.176970748</v>
+        <v>58.821213435</v>
       </c>
       <c r="O6">
-        <v>17.7530912244</v>
+        <v>17.6463640305</v>
       </c>
       <c r="P6">
-        <v>41.42387952360001</v>
+        <v>41.17484940450001</v>
       </c>
       <c r="Q6">
-        <v>44.7238795236</v>
+        <v>44.47484940450001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1051056889837138</v>
+        <v>0.1055479858331556</v>
       </c>
       <c r="T6">
-        <v>0.5735313387665358</v>
+        <v>0.5778086873403327</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>42.5852103284803</v>
+        <v>34.06816826278424</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1020310865414978</v>
+        <v>0.1017523116586303</v>
       </c>
       <c r="C7">
-        <v>688.9096277039361</v>
+        <v>685.3368960252387</v>
       </c>
       <c r="D7">
-        <v>702.4731777039361</v>
+        <v>705.9731560252387</v>
       </c>
       <c r="E7">
-        <v>35.29255000000001</v>
+        <v>42.36526000000001</v>
       </c>
       <c r="F7">
-        <v>35.36355</v>
+        <v>42.43626</v>
       </c>
       <c r="G7">
         <v>21.8</v>
@@ -1861,28 +1861,28 @@
         <v>60.6</v>
       </c>
       <c r="M7">
-        <v>1.778786565</v>
+        <v>2.134543878</v>
       </c>
       <c r="N7">
-        <v>58.821213435</v>
+        <v>58.465456122</v>
       </c>
       <c r="O7">
-        <v>17.6463640305</v>
+        <v>17.5396368366</v>
       </c>
       <c r="P7">
-        <v>41.17484940450001</v>
+        <v>40.9258192854</v>
       </c>
       <c r="Q7">
-        <v>44.47484940450001</v>
+        <v>44.22581928539999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1055479858331556</v>
+        <v>0.105999693253862</v>
       </c>
       <c r="T7">
-        <v>0.5778086873403327</v>
+        <v>0.5821770433305934</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>34.06816826278424</v>
+        <v>28.39014021898687</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1017523116586303</v>
+        <v>0.1014735367757628</v>
       </c>
       <c r="C8">
-        <v>685.3368960252387</v>
+        <v>681.7992153277818</v>
       </c>
       <c r="D8">
-        <v>705.9731560252387</v>
+        <v>709.5081853277818</v>
       </c>
       <c r="E8">
-        <v>42.36526000000001</v>
+        <v>49.43797</v>
       </c>
       <c r="F8">
-        <v>42.43626</v>
+        <v>49.50897</v>
       </c>
       <c r="G8">
         <v>21.8</v>
@@ -1943,28 +1943,28 @@
         <v>60.6</v>
       </c>
       <c r="M8">
-        <v>2.134543878</v>
+        <v>2.490301191</v>
       </c>
       <c r="N8">
-        <v>58.465456122</v>
+        <v>58.109698809</v>
       </c>
       <c r="O8">
-        <v>17.5396368366</v>
+        <v>17.4329096427</v>
       </c>
       <c r="P8">
-        <v>40.9258192854</v>
+        <v>40.6767891663</v>
       </c>
       <c r="Q8">
-        <v>44.22581928539999</v>
+        <v>43.97678916629999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.105999693253862</v>
+        <v>0.1064611148126481</v>
       </c>
       <c r="T8">
-        <v>0.5821770433305934</v>
+        <v>0.5866393424604296</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>28.39014021898687</v>
+        <v>24.33440590198875</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1014735367757628</v>
+        <v>0.1011947618928953</v>
       </c>
       <c r="C9">
-        <v>681.7992153277821</v>
+        <v>678.2971147951664</v>
       </c>
       <c r="D9">
-        <v>709.5081853277821</v>
+        <v>713.0787947951665</v>
       </c>
       <c r="E9">
-        <v>49.43797000000001</v>
+        <v>56.51068000000001</v>
       </c>
       <c r="F9">
-        <v>49.50897000000001</v>
+        <v>56.58168000000001</v>
       </c>
       <c r="G9">
         <v>21.8</v>
@@ -2025,28 +2025,28 @@
         <v>60.6</v>
       </c>
       <c r="M9">
-        <v>2.490301191</v>
+        <v>2.846058504</v>
       </c>
       <c r="N9">
-        <v>58.109698809</v>
+        <v>57.753941496</v>
       </c>
       <c r="O9">
-        <v>17.4329096427</v>
+        <v>17.3261824488</v>
       </c>
       <c r="P9">
-        <v>40.6767891663</v>
+        <v>40.4277590472</v>
       </c>
       <c r="Q9">
-        <v>43.97678916629999</v>
+        <v>43.7277590472</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1064611148126481</v>
+        <v>0.1069325672748862</v>
       </c>
       <c r="T9">
-        <v>0.5866393424604296</v>
+        <v>0.5911986480930883</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>24.33440590198874</v>
+        <v>21.29260516424015</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1011947618928953</v>
+        <v>0.1009159870100278</v>
       </c>
       <c r="C10">
-        <v>678.2971147951664</v>
+        <v>674.8311343173677</v>
       </c>
       <c r="D10">
-        <v>713.0787947951665</v>
+        <v>716.6855243173678</v>
       </c>
       <c r="E10">
-        <v>56.51068000000001</v>
+        <v>63.58339000000001</v>
       </c>
       <c r="F10">
-        <v>56.58168000000001</v>
+        <v>63.65439000000001</v>
       </c>
       <c r="G10">
         <v>21.8</v>
@@ -2107,28 +2107,28 @@
         <v>60.6</v>
       </c>
       <c r="M10">
-        <v>2.846058504</v>
+        <v>3.201815817</v>
       </c>
       <c r="N10">
-        <v>57.753941496</v>
+        <v>57.398184183</v>
       </c>
       <c r="O10">
-        <v>17.3261824488</v>
+        <v>17.2194552549</v>
       </c>
       <c r="P10">
-        <v>40.4277590472</v>
+        <v>40.1787289281</v>
       </c>
       <c r="Q10">
-        <v>43.7277590472</v>
+        <v>43.4787289281</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1069325672748862</v>
+        <v>0.1074143813297008</v>
       </c>
       <c r="T10">
-        <v>0.5911986480930883</v>
+        <v>0.595858158245146</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.29260516424015</v>
+        <v>18.92676014599125</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1009159870100278</v>
+        <v>0.1006372121271602</v>
       </c>
       <c r="C11">
-        <v>674.8311343173677</v>
+        <v>671.401824762874</v>
       </c>
       <c r="D11">
-        <v>716.6855243173678</v>
+        <v>720.3289247628741</v>
       </c>
       <c r="E11">
-        <v>63.58339000000001</v>
+        <v>70.65610000000001</v>
       </c>
       <c r="F11">
-        <v>63.65439000000001</v>
+        <v>70.72710000000001</v>
       </c>
       <c r="G11">
         <v>21.8</v>
@@ -2189,28 +2189,28 @@
         <v>60.6</v>
       </c>
       <c r="M11">
-        <v>3.201815817</v>
+        <v>3.55757313</v>
       </c>
       <c r="N11">
-        <v>57.398184183</v>
+        <v>57.04242687</v>
       </c>
       <c r="O11">
-        <v>17.2194552549</v>
+        <v>17.112728061</v>
       </c>
       <c r="P11">
-        <v>40.1787289281</v>
+        <v>39.929698809</v>
       </c>
       <c r="Q11">
-        <v>43.4787289281</v>
+        <v>43.229698809</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1074143813297008</v>
+        <v>0.1079069023635114</v>
       </c>
       <c r="T11">
-        <v>0.595858158245146</v>
+        <v>0.6006212130672495</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.92676014599125</v>
+        <v>17.03408413139212</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1006372121271602</v>
+        <v>0.1003584372442928</v>
       </c>
       <c r="C12">
-        <v>671.401824762874</v>
+        <v>668.0097482591686</v>
       </c>
       <c r="D12">
-        <v>720.3289247628741</v>
+        <v>724.0095582591687</v>
       </c>
       <c r="E12">
-        <v>70.65610000000001</v>
+        <v>77.72881000000001</v>
       </c>
       <c r="F12">
-        <v>70.72710000000001</v>
+        <v>77.79981000000001</v>
       </c>
       <c r="G12">
         <v>21.8</v>
@@ -2271,28 +2271,28 @@
         <v>60.6</v>
       </c>
       <c r="M12">
-        <v>3.55757313</v>
+        <v>3.913330443</v>
       </c>
       <c r="N12">
-        <v>57.04242687</v>
+        <v>56.686669557</v>
       </c>
       <c r="O12">
-        <v>17.112728061</v>
+        <v>17.0060008671</v>
       </c>
       <c r="P12">
-        <v>39.929698809</v>
+        <v>39.6806686899</v>
       </c>
       <c r="Q12">
-        <v>43.229698809</v>
+        <v>42.9806686899</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1079069023635114</v>
+        <v>0.1084104912857222</v>
       </c>
       <c r="T12">
-        <v>0.6006212130672495</v>
+        <v>0.6054913028291755</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.03408413139212</v>
+        <v>15.48553102853829</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1003584372442928</v>
+        <v>0.1000796623614252</v>
       </c>
       <c r="C13">
-        <v>668.0097482591686</v>
+        <v>664.6554784818571</v>
       </c>
       <c r="D13">
-        <v>724.0095582591687</v>
+        <v>727.7279984818572</v>
       </c>
       <c r="E13">
-        <v>77.72881000000001</v>
+        <v>84.80152000000001</v>
       </c>
       <c r="F13">
-        <v>77.79981000000001</v>
+        <v>84.87252000000001</v>
       </c>
       <c r="G13">
         <v>21.8</v>
@@ -2353,28 +2353,28 @@
         <v>60.6</v>
       </c>
       <c r="M13">
-        <v>3.913330443</v>
+        <v>4.269087756</v>
       </c>
       <c r="N13">
-        <v>56.686669557</v>
+        <v>56.330912244</v>
       </c>
       <c r="O13">
-        <v>17.0060008671</v>
+        <v>16.8992736732</v>
       </c>
       <c r="P13">
-        <v>39.6806686899</v>
+        <v>39.4316385708</v>
       </c>
       <c r="Q13">
-        <v>42.9806686899</v>
+        <v>42.7316385708</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1084104912857222</v>
+        <v>0.1089255254107105</v>
       </c>
       <c r="T13">
-        <v>0.6054913028291755</v>
+        <v>0.6104720764493271</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.48553102853829</v>
+        <v>14.19507010949343</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1000796623614252</v>
+        <v>0.09980088747855775</v>
       </c>
       <c r="C14">
-        <v>664.6554784818571</v>
+        <v>661.3396009527439</v>
       </c>
       <c r="D14">
-        <v>727.7279984818572</v>
+        <v>731.484830952744</v>
       </c>
       <c r="E14">
-        <v>84.80152000000001</v>
+        <v>91.87423000000001</v>
       </c>
       <c r="F14">
-        <v>84.87252000000001</v>
+        <v>91.94523000000001</v>
       </c>
       <c r="G14">
         <v>21.8</v>
@@ -2435,28 +2435,28 @@
         <v>60.6</v>
       </c>
       <c r="M14">
-        <v>4.269087756</v>
+        <v>4.624845069</v>
       </c>
       <c r="N14">
-        <v>56.330912244</v>
+        <v>55.975154931</v>
       </c>
       <c r="O14">
-        <v>16.8992736732</v>
+        <v>16.7925464793</v>
       </c>
       <c r="P14">
-        <v>39.4316385708</v>
+        <v>39.1826084517</v>
       </c>
       <c r="Q14">
-        <v>42.7316385708</v>
+        <v>42.4826084517</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1089255254107105</v>
+        <v>0.1094523994006411</v>
       </c>
       <c r="T14">
-        <v>0.6104720764493271</v>
+        <v>0.6155673506124707</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.19507010949343</v>
+        <v>13.1031416395324</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09980088747855775</v>
+        <v>0.09966911259569021</v>
       </c>
       <c r="C15">
-        <v>661.3396009527439</v>
+        <v>656.0562526717988</v>
       </c>
       <c r="D15">
-        <v>731.484830952744</v>
+        <v>733.2741926717989</v>
       </c>
       <c r="E15">
-        <v>91.87423000000001</v>
+        <v>98.94694000000003</v>
       </c>
       <c r="F15">
-        <v>91.94523000000001</v>
+        <v>99.01794000000002</v>
       </c>
       <c r="G15">
         <v>21.8</v>
@@ -2517,45 +2517,45 @@
         <v>60.6</v>
       </c>
       <c r="M15">
-        <v>4.624845069</v>
+        <v>5.129129292000001</v>
       </c>
       <c r="N15">
-        <v>55.975154931</v>
+        <v>55.470870708</v>
       </c>
       <c r="O15">
-        <v>16.7925464793</v>
+        <v>16.6412612124</v>
       </c>
       <c r="P15">
-        <v>39.1826084517</v>
+        <v>38.8296094956</v>
       </c>
       <c r="Q15">
-        <v>42.4826084517</v>
+        <v>42.12960949559999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1094523994006411</v>
+        <v>0.1099915262740584</v>
       </c>
       <c r="T15">
-        <v>0.6155673506124707</v>
+        <v>0.6207811195235944</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.1031416395324</v>
+        <v>11.81487081920882</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09966911259569021</v>
+        <v>0.09940083771282272</v>
       </c>
       <c r="C16">
-        <v>656.0562526717988</v>
+        <v>652.6536168076314</v>
       </c>
       <c r="D16">
-        <v>733.2741926717989</v>
+        <v>736.9442668076314</v>
       </c>
       <c r="E16">
-        <v>98.94694000000003</v>
+        <v>106.01965</v>
       </c>
       <c r="F16">
-        <v>99.01794000000002</v>
+        <v>106.09065</v>
       </c>
       <c r="G16">
         <v>21.8</v>
@@ -2599,28 +2599,28 @@
         <v>60.6</v>
       </c>
       <c r="M16">
-        <v>5.129129292000001</v>
+        <v>5.495495670000001</v>
       </c>
       <c r="N16">
-        <v>55.470870708</v>
+        <v>55.10450433</v>
       </c>
       <c r="O16">
-        <v>16.6412612124</v>
+        <v>16.531351299</v>
       </c>
       <c r="P16">
-        <v>38.8296094956</v>
+        <v>38.573153031</v>
       </c>
       <c r="Q16">
-        <v>42.12960949559999</v>
+        <v>41.873153031</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1099915262740584</v>
+        <v>0.1105433384856738</v>
       </c>
       <c r="T16">
-        <v>0.6207811195235944</v>
+        <v>0.6261175653502741</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.81487081920882</v>
+        <v>11.0272127645949</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09940083771282272</v>
+        <v>0.09913256282995522</v>
       </c>
       <c r="C17">
-        <v>652.6536168076314</v>
+        <v>649.2879035534664</v>
       </c>
       <c r="D17">
-        <v>736.9442668076314</v>
+        <v>740.6512635534665</v>
       </c>
       <c r="E17">
-        <v>106.01965</v>
+        <v>113.09236</v>
       </c>
       <c r="F17">
-        <v>106.09065</v>
+        <v>113.16336</v>
       </c>
       <c r="G17">
         <v>21.8</v>
@@ -2681,28 +2681,28 @@
         <v>60.6</v>
       </c>
       <c r="M17">
-        <v>5.49549567</v>
+        <v>5.861862048000001</v>
       </c>
       <c r="N17">
-        <v>55.10450433</v>
+        <v>54.738137952</v>
       </c>
       <c r="O17">
-        <v>16.531351299</v>
+        <v>16.4214413856</v>
       </c>
       <c r="P17">
-        <v>38.573153031</v>
+        <v>38.3166965664</v>
       </c>
       <c r="Q17">
-        <v>41.873153031</v>
+        <v>41.61669656639999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1105433384856738</v>
+        <v>0.11110828908328</v>
       </c>
       <c r="T17">
-        <v>0.6261175653502741</v>
+        <v>0.6315810694109221</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.0272127645949</v>
+        <v>10.33801196680772</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09913256282995522</v>
+        <v>0.0990665879470877</v>
       </c>
       <c r="C18">
-        <v>649.2879035534664</v>
+        <v>643.1325487331742</v>
       </c>
       <c r="D18">
-        <v>740.6512635534665</v>
+        <v>741.5686187331743</v>
       </c>
       <c r="E18">
-        <v>113.09236</v>
+        <v>120.16507</v>
       </c>
       <c r="F18">
-        <v>113.16336</v>
+        <v>120.23607</v>
       </c>
       <c r="G18">
         <v>21.8</v>
@@ -2763,45 +2763,45 @@
         <v>60.6</v>
       </c>
       <c r="M18">
-        <v>5.861862048000001</v>
+        <v>6.432629745000002</v>
       </c>
       <c r="N18">
-        <v>54.738137952</v>
+        <v>54.167370255</v>
       </c>
       <c r="O18">
-        <v>16.4214413856</v>
+        <v>16.2502110765</v>
       </c>
       <c r="P18">
-        <v>38.3166965664</v>
+        <v>37.9171591785</v>
       </c>
       <c r="Q18">
-        <v>41.61669656639999</v>
+        <v>41.2171591785</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.11110828908328</v>
+        <v>0.1116868529482984</v>
       </c>
       <c r="T18">
-        <v>0.6315810694109221</v>
+        <v>0.6371762241718268</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.33801196680772</v>
+        <v>9.420719426157488</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0990665879470877</v>
+        <v>0.09881021306422018</v>
       </c>
       <c r="C19">
-        <v>643.1325487331742</v>
+        <v>639.6463092786825</v>
       </c>
       <c r="D19">
-        <v>741.5686187331743</v>
+        <v>745.1550892786826</v>
       </c>
       <c r="E19">
-        <v>120.16507</v>
+        <v>127.23778</v>
       </c>
       <c r="F19">
-        <v>120.23607</v>
+        <v>127.30878</v>
       </c>
       <c r="G19">
         <v>21.8</v>
@@ -2845,28 +2845,28 @@
         <v>60.6</v>
       </c>
       <c r="M19">
-        <v>6.432629745000002</v>
+        <v>6.811019730000002</v>
       </c>
       <c r="N19">
-        <v>54.167370255</v>
+        <v>53.78898027</v>
       </c>
       <c r="O19">
-        <v>16.2502110765</v>
+        <v>16.136694081</v>
       </c>
       <c r="P19">
-        <v>37.9171591785</v>
+        <v>37.65228618899999</v>
       </c>
       <c r="Q19">
-        <v>41.2171591785</v>
+        <v>40.95228618899999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1116868529482984</v>
+        <v>0.1122795281270978</v>
       </c>
       <c r="T19">
-        <v>0.6371762241718268</v>
+        <v>0.6429078461220218</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.420719426157488</v>
+        <v>8.897346124704294</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09881021306422019</v>
+        <v>0.09855383818135272</v>
       </c>
       <c r="C20">
-        <v>639.6463092786823</v>
+        <v>636.194929125341</v>
       </c>
       <c r="D20">
-        <v>745.1550892786825</v>
+        <v>748.776419125341</v>
       </c>
       <c r="E20">
-        <v>127.23778</v>
+        <v>134.31049</v>
       </c>
       <c r="F20">
-        <v>127.30878</v>
+        <v>134.38149</v>
       </c>
       <c r="G20">
         <v>21.8</v>
@@ -2927,28 +2927,28 @@
         <v>60.6</v>
       </c>
       <c r="M20">
-        <v>6.811019730000001</v>
+        <v>7.189409715000001</v>
       </c>
       <c r="N20">
-        <v>53.78898027</v>
+        <v>53.410590285</v>
       </c>
       <c r="O20">
-        <v>16.136694081</v>
+        <v>16.0231770855</v>
       </c>
       <c r="P20">
-        <v>37.652286189</v>
+        <v>37.3874131995</v>
       </c>
       <c r="Q20">
-        <v>40.952286189</v>
+        <v>40.6874131995</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1122795281270978</v>
+        <v>0.1128868372609293</v>
       </c>
       <c r="T20">
-        <v>0.6429078461220218</v>
+        <v>0.6487809896018514</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.897346124704296</v>
+        <v>8.429064749719858</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09855383818135272</v>
+        <v>0.0982974632984852</v>
       </c>
       <c r="C21">
-        <v>636.194929125341</v>
+        <v>632.7789189863561</v>
       </c>
       <c r="D21">
-        <v>748.776419125341</v>
+        <v>752.4331189863561</v>
       </c>
       <c r="E21">
-        <v>134.31049</v>
+        <v>141.3832</v>
       </c>
       <c r="F21">
-        <v>134.38149</v>
+        <v>141.4542</v>
       </c>
       <c r="G21">
         <v>21.8</v>
@@ -3009,28 +3009,28 @@
         <v>60.6</v>
       </c>
       <c r="M21">
-        <v>7.189409715000001</v>
+        <v>7.567799700000001</v>
       </c>
       <c r="N21">
-        <v>53.410590285</v>
+        <v>53.0322003</v>
       </c>
       <c r="O21">
-        <v>16.0231770855</v>
+        <v>15.90966009</v>
       </c>
       <c r="P21">
-        <v>37.3874131995</v>
+        <v>37.12254021</v>
       </c>
       <c r="Q21">
-        <v>40.6874131995</v>
+        <v>40.42254020999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1128868372609293</v>
+        <v>0.1135093291231065</v>
       </c>
       <c r="T21">
-        <v>0.6487809896018514</v>
+        <v>0.6548009616686766</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.429064749719858</v>
+        <v>8.007611512233865</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0982974632984852</v>
+        <v>0.09804108841561769</v>
       </c>
       <c r="C22">
-        <v>632.7789189863561</v>
+        <v>629.3987996003007</v>
       </c>
       <c r="D22">
-        <v>752.4331189863561</v>
+        <v>756.1257096003008</v>
       </c>
       <c r="E22">
-        <v>141.3832</v>
+        <v>148.45591</v>
       </c>
       <c r="F22">
-        <v>141.4542</v>
+        <v>148.52691</v>
       </c>
       <c r="G22">
         <v>21.8</v>
@@ -3091,28 +3091,28 @@
         <v>60.6</v>
       </c>
       <c r="M22">
-        <v>7.567799700000001</v>
+        <v>7.946189685</v>
       </c>
       <c r="N22">
-        <v>53.0322003</v>
+        <v>52.653810315</v>
       </c>
       <c r="O22">
-        <v>15.90966009</v>
+        <v>15.7961430945</v>
       </c>
       <c r="P22">
-        <v>37.12254021</v>
+        <v>36.85766722050001</v>
       </c>
       <c r="Q22">
-        <v>40.42254020999999</v>
+        <v>40.1576672205</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1135093291231065</v>
+        <v>0.1141475802729338</v>
       </c>
       <c r="T22">
-        <v>0.6548009616686766</v>
+        <v>0.6609733380916241</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.007611512233865</v>
+        <v>7.626296678317968</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09804108841561769</v>
+        <v>0.09790791353275019</v>
       </c>
       <c r="C23">
-        <v>629.3987996003007</v>
+        <v>624.258559084918</v>
       </c>
       <c r="D23">
-        <v>756.1257096003008</v>
+        <v>758.0581790849182</v>
       </c>
       <c r="E23">
-        <v>148.45591</v>
+        <v>155.52862</v>
       </c>
       <c r="F23">
-        <v>148.52691</v>
+        <v>155.59962</v>
       </c>
       <c r="G23">
         <v>21.8</v>
@@ -3173,45 +3173,45 @@
         <v>60.6</v>
       </c>
       <c r="M23">
-        <v>7.946189685</v>
+        <v>8.449059366</v>
       </c>
       <c r="N23">
-        <v>52.653810315</v>
+        <v>52.150940634</v>
       </c>
       <c r="O23">
-        <v>15.7961430945</v>
+        <v>15.6452821902</v>
       </c>
       <c r="P23">
-        <v>36.85766722050001</v>
+        <v>36.5056584438</v>
       </c>
       <c r="Q23">
-        <v>40.1576672205</v>
+        <v>39.8056584438</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1141475802729338</v>
+        <v>0.1148021968368592</v>
       </c>
       <c r="T23">
-        <v>0.660973338091624</v>
+        <v>0.6673039805766983</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.626296678317968</v>
+        <v>7.172396047287993</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09790791353275019</v>
+        <v>0.09765713864988267</v>
       </c>
       <c r="C24">
-        <v>624.258559084918</v>
+        <v>620.8517272266004</v>
       </c>
       <c r="D24">
-        <v>758.0581790849182</v>
+        <v>761.7240572266004</v>
       </c>
       <c r="E24">
-        <v>155.52862</v>
+        <v>162.60133</v>
       </c>
       <c r="F24">
-        <v>155.59962</v>
+        <v>162.67233</v>
       </c>
       <c r="G24">
         <v>21.8</v>
@@ -3255,28 +3255,28 @@
         <v>60.6</v>
       </c>
       <c r="M24">
-        <v>8.449059366</v>
+        <v>8.833107519</v>
       </c>
       <c r="N24">
-        <v>52.150940634</v>
+        <v>51.766892481</v>
       </c>
       <c r="O24">
-        <v>15.6452821902</v>
+        <v>15.5300677443</v>
       </c>
       <c r="P24">
-        <v>36.5056584438</v>
+        <v>36.2368247367</v>
       </c>
       <c r="Q24">
-        <v>39.8056584438</v>
+        <v>39.5368247367</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1148021968368592</v>
+        <v>0.1154738164284191</v>
       </c>
       <c r="T24">
-        <v>0.6673039805766983</v>
+        <v>0.6737990553341121</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.172396047287993</v>
+        <v>6.860552740884168</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09765713864988267</v>
+        <v>0.09740636376701518</v>
       </c>
       <c r="C25">
-        <v>620.8517272266004</v>
+        <v>617.4805231511552</v>
       </c>
       <c r="D25">
-        <v>761.7240572266004</v>
+        <v>765.4255631511553</v>
       </c>
       <c r="E25">
-        <v>162.60133</v>
+        <v>169.67404</v>
       </c>
       <c r="F25">
-        <v>162.67233</v>
+        <v>169.74504</v>
       </c>
       <c r="G25">
         <v>21.8</v>
@@ -3337,28 +3337,28 @@
         <v>60.6</v>
       </c>
       <c r="M25">
-        <v>8.833107519</v>
+        <v>9.217155672000001</v>
       </c>
       <c r="N25">
-        <v>51.766892481</v>
+        <v>51.382844328</v>
       </c>
       <c r="O25">
-        <v>15.5300677443</v>
+        <v>15.4148532984</v>
       </c>
       <c r="P25">
-        <v>36.2368247367</v>
+        <v>35.9679910296</v>
       </c>
       <c r="Q25">
-        <v>39.5368247367</v>
+        <v>39.2679910296</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1154738164284191</v>
+        <v>0.1161631102197568</v>
       </c>
       <c r="T25">
-        <v>0.6737990553341121</v>
+        <v>0.6804650531114579</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.860552740884168</v>
+        <v>6.574696376680661</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09740636376701518</v>
+        <v>0.09715558888414767</v>
       </c>
       <c r="C26">
-        <v>617.4805231511552</v>
+        <v>614.1454687815102</v>
       </c>
       <c r="D26">
-        <v>765.4255631511553</v>
+        <v>769.1632187815103</v>
       </c>
       <c r="E26">
-        <v>169.67404</v>
+        <v>176.74675</v>
       </c>
       <c r="F26">
-        <v>169.74504</v>
+        <v>176.81775</v>
       </c>
       <c r="G26">
         <v>21.8</v>
@@ -3419,28 +3419,28 @@
         <v>60.6</v>
       </c>
       <c r="M26">
-        <v>9.217155672000001</v>
+        <v>9.601203825000001</v>
       </c>
       <c r="N26">
-        <v>51.382844328</v>
+        <v>50.998796175</v>
       </c>
       <c r="O26">
-        <v>15.4148532984</v>
+        <v>15.2996388525</v>
       </c>
       <c r="P26">
-        <v>35.9679910296</v>
+        <v>35.6991573225</v>
       </c>
       <c r="Q26">
-        <v>39.2679910296</v>
+        <v>38.9991573225</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1161631102197568</v>
+        <v>0.1168707851788636</v>
       </c>
       <c r="T26">
-        <v>0.6804650531114579</v>
+        <v>0.687308810829533</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.574696376680661</v>
+        <v>6.311708521613435</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09715558888414767</v>
+        <v>0.09708681400128014</v>
       </c>
       <c r="C27">
-        <v>614.1454687815102</v>
+        <v>608.1041956392646</v>
       </c>
       <c r="D27">
-        <v>769.1632187815103</v>
+        <v>770.1946556392647</v>
       </c>
       <c r="E27">
-        <v>176.74675</v>
+        <v>183.81946</v>
       </c>
       <c r="F27">
-        <v>176.81775</v>
+        <v>183.89046</v>
       </c>
       <c r="G27">
         <v>21.8</v>
@@ -3501,45 +3501,45 @@
         <v>60.6</v>
       </c>
       <c r="M27">
-        <v>9.601203825000001</v>
+        <v>10.169142438</v>
       </c>
       <c r="N27">
-        <v>50.998796175</v>
+        <v>50.430857562</v>
       </c>
       <c r="O27">
-        <v>15.2996388525</v>
+        <v>15.1292572686</v>
       </c>
       <c r="P27">
-        <v>35.6991573225</v>
+        <v>35.3016002934</v>
       </c>
       <c r="Q27">
-        <v>38.9991573225</v>
+        <v>38.6016002934</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1168707851788636</v>
+        <v>0.1175975864882164</v>
       </c>
       <c r="T27">
-        <v>0.687308810829533</v>
+        <v>0.6943375349724207</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.311708521613435</v>
+        <v>5.959204561197827</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09708681400128014</v>
+        <v>0.09684303911841266</v>
       </c>
       <c r="C28">
-        <v>608.1041956392646</v>
+        <v>604.7098346405469</v>
       </c>
       <c r="D28">
-        <v>770.1946556392647</v>
+        <v>773.8730046405469</v>
       </c>
       <c r="E28">
-        <v>183.81946</v>
+        <v>190.89217</v>
       </c>
       <c r="F28">
-        <v>183.89046</v>
+        <v>190.96317</v>
       </c>
       <c r="G28">
         <v>21.8</v>
@@ -3583,28 +3583,28 @@
         <v>60.6</v>
       </c>
       <c r="M28">
-        <v>10.169142438</v>
+        <v>10.560263301</v>
       </c>
       <c r="N28">
-        <v>50.430857562</v>
+        <v>50.039736699</v>
       </c>
       <c r="O28">
-        <v>15.1292572686</v>
+        <v>15.0119210097</v>
       </c>
       <c r="P28">
-        <v>35.3016002934</v>
+        <v>35.0278156893</v>
       </c>
       <c r="Q28">
-        <v>38.6016002934</v>
+        <v>38.3278156893</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1175975864882164</v>
+        <v>0.1183443001622091</v>
       </c>
       <c r="T28">
-        <v>0.6943375349724207</v>
+        <v>0.7015588269000453</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.959204561197827</v>
+        <v>5.738493281153464</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09684303911841266</v>
+        <v>0.09659926423554514</v>
       </c>
       <c r="C29">
-        <v>604.7098346405469</v>
+        <v>601.3507768734975</v>
       </c>
       <c r="D29">
-        <v>773.8730046405469</v>
+        <v>777.5866568734975</v>
       </c>
       <c r="E29">
-        <v>190.89217</v>
+        <v>197.9648800000001</v>
       </c>
       <c r="F29">
-        <v>190.96317</v>
+        <v>198.03588</v>
       </c>
       <c r="G29">
         <v>21.8</v>
@@ -3665,28 +3665,28 @@
         <v>60.6</v>
       </c>
       <c r="M29">
-        <v>10.560263301</v>
+        <v>10.951384164</v>
       </c>
       <c r="N29">
-        <v>50.039736699</v>
+        <v>49.648615836</v>
       </c>
       <c r="O29">
-        <v>15.0119210097</v>
+        <v>14.8945847508</v>
       </c>
       <c r="P29">
-        <v>35.0278156893</v>
+        <v>34.7540310852</v>
       </c>
       <c r="Q29">
-        <v>38.3278156893</v>
+        <v>38.05403108519999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1183443001622091</v>
+        <v>0.1191117558827016</v>
       </c>
       <c r="T29">
-        <v>0.7015588269000453</v>
+        <v>0.7089807102701037</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.738493281153464</v>
+        <v>5.533547092540839</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09659926423554514</v>
+        <v>0.09635548935267764</v>
       </c>
       <c r="C30">
-        <v>601.3507768734975</v>
+        <v>598.0275330269416</v>
       </c>
       <c r="D30">
-        <v>777.5866568734975</v>
+        <v>781.3361230269417</v>
       </c>
       <c r="E30">
-        <v>197.9648800000001</v>
+        <v>205.0375900000001</v>
       </c>
       <c r="F30">
-        <v>198.03588</v>
+        <v>205.10859</v>
       </c>
       <c r="G30">
         <v>21.8</v>
@@ -3747,28 +3747,28 @@
         <v>60.6</v>
       </c>
       <c r="M30">
-        <v>10.951384164</v>
+        <v>11.342505027</v>
       </c>
       <c r="N30">
-        <v>49.648615836</v>
+        <v>49.257494973</v>
       </c>
       <c r="O30">
-        <v>14.8945847508</v>
+        <v>14.7772484919</v>
       </c>
       <c r="P30">
-        <v>34.7540310852</v>
+        <v>34.4802464811</v>
       </c>
       <c r="Q30">
-        <v>38.05403108519999</v>
+        <v>37.78024648109999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1191117558827016</v>
+        <v>0.1199008300741939</v>
       </c>
       <c r="T30">
-        <v>0.7089807102701037</v>
+        <v>0.7166116607773471</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.533547092540839</v>
+        <v>5.342735123832534</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09635548935267764</v>
+        <v>0.09611171446981012</v>
       </c>
       <c r="C31">
-        <v>598.0275330269416</v>
+        <v>594.7406236874488</v>
       </c>
       <c r="D31">
-        <v>781.3361230269417</v>
+        <v>785.1219236874489</v>
       </c>
       <c r="E31">
-        <v>205.03759</v>
+        <v>212.1103</v>
       </c>
       <c r="F31">
-        <v>205.10859</v>
+        <v>212.1813</v>
       </c>
       <c r="G31">
         <v>21.8</v>
@@ -3829,28 +3829,28 @@
         <v>60.6</v>
       </c>
       <c r="M31">
-        <v>11.342505027</v>
+        <v>11.73362589</v>
       </c>
       <c r="N31">
-        <v>49.257494973</v>
+        <v>48.86637411</v>
       </c>
       <c r="O31">
-        <v>14.7772484919</v>
+        <v>14.659912233</v>
       </c>
       <c r="P31">
-        <v>34.4802464811</v>
+        <v>34.206461877</v>
       </c>
       <c r="Q31">
-        <v>37.78024648109999</v>
+        <v>37.506461877</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1199008300741939</v>
+        <v>0.1207124492425859</v>
       </c>
       <c r="T31">
-        <v>0.7166116607773471</v>
+        <v>0.7244606384419401</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.342735123832535</v>
+        <v>5.164643953038118</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09611171446981012</v>
+        <v>0.09586793958694262</v>
       </c>
       <c r="C32">
-        <v>594.7406236874488</v>
+        <v>591.4905795802854</v>
       </c>
       <c r="D32">
-        <v>785.1219236874489</v>
+        <v>788.9445895802854</v>
       </c>
       <c r="E32">
-        <v>212.1103</v>
+        <v>219.18301</v>
       </c>
       <c r="F32">
-        <v>212.1813</v>
+        <v>219.25401</v>
       </c>
       <c r="G32">
         <v>21.8</v>
@@ -3911,28 +3911,28 @@
         <v>60.6</v>
       </c>
       <c r="M32">
-        <v>11.73362589</v>
+        <v>12.124746753</v>
       </c>
       <c r="N32">
-        <v>48.86637411</v>
+        <v>48.475253247</v>
       </c>
       <c r="O32">
-        <v>14.659912233</v>
+        <v>14.5425759741</v>
       </c>
       <c r="P32">
-        <v>34.206461877</v>
+        <v>33.9326772729</v>
       </c>
       <c r="Q32">
-        <v>37.506461877</v>
+        <v>37.2326772729</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1207124492425859</v>
+        <v>0.1215475936042647</v>
       </c>
       <c r="T32">
-        <v>0.7244606384419401</v>
+        <v>0.7325371227055069</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.164643953038118</v>
+        <v>4.998042535198177</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09586793958694262</v>
+        <v>0.09562416470407512</v>
       </c>
       <c r="C33">
-        <v>591.4905795802854</v>
+        <v>588.2779418174455</v>
       </c>
       <c r="D33">
-        <v>788.9445895802854</v>
+        <v>792.8046618174455</v>
       </c>
       <c r="E33">
-        <v>219.18301</v>
+        <v>226.25572</v>
       </c>
       <c r="F33">
-        <v>219.25401</v>
+        <v>226.32672</v>
       </c>
       <c r="G33">
         <v>21.8</v>
@@ -3993,28 +3993,28 @@
         <v>60.6</v>
       </c>
       <c r="M33">
-        <v>12.124746753</v>
+        <v>12.515867616</v>
       </c>
       <c r="N33">
-        <v>48.475253247</v>
+        <v>48.084132384</v>
       </c>
       <c r="O33">
-        <v>14.5425759741</v>
+        <v>14.4252397152</v>
       </c>
       <c r="P33">
-        <v>33.9326772729</v>
+        <v>33.6588926688</v>
       </c>
       <c r="Q33">
-        <v>37.2326772729</v>
+        <v>36.9588926688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1215475936042647</v>
+        <v>0.1224073010354046</v>
       </c>
       <c r="T33">
-        <v>0.7325371227055069</v>
+        <v>0.7408511506238844</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.998042535198177</v>
+        <v>4.841853705973235</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09562416470407512</v>
+        <v>0.09538038982120761</v>
       </c>
       <c r="C34">
-        <v>588.2779418174455</v>
+        <v>585.1032621529934</v>
       </c>
       <c r="D34">
-        <v>792.8046618174455</v>
+        <v>796.7026921529934</v>
       </c>
       <c r="E34">
-        <v>226.25572</v>
+        <v>233.32843</v>
       </c>
       <c r="F34">
-        <v>226.32672</v>
+        <v>233.39943</v>
       </c>
       <c r="G34">
         <v>21.8</v>
@@ -4075,28 +4075,28 @@
         <v>60.6</v>
       </c>
       <c r="M34">
-        <v>12.515867616</v>
+        <v>12.906988479</v>
       </c>
       <c r="N34">
-        <v>48.084132384</v>
+        <v>47.693011521</v>
       </c>
       <c r="O34">
-        <v>14.4252397152</v>
+        <v>14.3079034563</v>
       </c>
       <c r="P34">
-        <v>33.6588926688</v>
+        <v>33.38510806470001</v>
       </c>
       <c r="Q34">
-        <v>36.9588926688</v>
+        <v>36.6851080647</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1224073010354046</v>
+        <v>0.1232926713749367</v>
       </c>
       <c r="T34">
-        <v>0.7408511506238844</v>
+        <v>0.7494133584801241</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.841853705973235</v>
+        <v>4.695130866398288</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09538038982120761</v>
+        <v>0.09513661493834009</v>
       </c>
       <c r="C35">
-        <v>585.1032621529934</v>
+        <v>581.967103245981</v>
       </c>
       <c r="D35">
-        <v>796.7026921529934</v>
+        <v>800.6392432459811</v>
       </c>
       <c r="E35">
-        <v>233.32843</v>
+        <v>240.4011400000001</v>
       </c>
       <c r="F35">
-        <v>233.39943</v>
+        <v>240.4721400000001</v>
       </c>
       <c r="G35">
         <v>21.8</v>
@@ -4157,28 +4157,28 @@
         <v>60.6</v>
       </c>
       <c r="M35">
-        <v>12.906988479</v>
+        <v>13.298109342</v>
       </c>
       <c r="N35">
-        <v>47.693011521</v>
+        <v>47.301890658</v>
       </c>
       <c r="O35">
-        <v>14.3079034563</v>
+        <v>14.1905671974</v>
       </c>
       <c r="P35">
-        <v>33.38510806470001</v>
+        <v>33.1113234606</v>
       </c>
       <c r="Q35">
-        <v>36.6851080647</v>
+        <v>36.41132346059999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1232926713749367</v>
+        <v>0.1242048711186971</v>
       </c>
       <c r="T35">
-        <v>0.7494133584801241</v>
+        <v>0.7582350271804921</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.695130866398288</v>
+        <v>4.557038782092455</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09513661493834009</v>
+        <v>0.09550534005547259</v>
       </c>
       <c r="C36">
-        <v>581.967103245981</v>
+        <v>568.9550756914227</v>
       </c>
       <c r="D36">
-        <v>800.6392432459811</v>
+        <v>794.6999256914229</v>
       </c>
       <c r="E36">
-        <v>240.4011400000001</v>
+        <v>247.4738500000001</v>
       </c>
       <c r="F36">
-        <v>240.4721400000001</v>
+        <v>247.5448500000001</v>
       </c>
       <c r="G36">
         <v>21.8</v>
@@ -4239,45 +4239,45 @@
         <v>60.6</v>
       </c>
       <c r="M36">
-        <v>13.298109342</v>
+        <v>14.30809233</v>
       </c>
       <c r="N36">
-        <v>47.301890658</v>
+        <v>46.29190767</v>
       </c>
       <c r="O36">
-        <v>14.1905671974</v>
+        <v>13.887572301</v>
       </c>
       <c r="P36">
-        <v>33.1113234606</v>
+        <v>32.404335369</v>
       </c>
       <c r="Q36">
-        <v>36.41132346059999</v>
+        <v>35.704335369</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1242048711186971</v>
+        <v>0.1251451385468809</v>
       </c>
       <c r="T36">
-        <v>0.7582350271804921</v>
+        <v>0.7673281318408715</v>
       </c>
       <c r="U36">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>4.557038782092455</v>
+        <v>4.235365456297695</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09550534005547259</v>
+        <v>0.09527906517260509</v>
       </c>
       <c r="C37">
-        <v>568.9550756914227</v>
+        <v>565.5166427735251</v>
       </c>
       <c r="D37">
-        <v>794.6999256914229</v>
+        <v>798.3342027735251</v>
       </c>
       <c r="E37">
-        <v>247.4738500000001</v>
+        <v>254.5465600000001</v>
       </c>
       <c r="F37">
-        <v>247.5448500000001</v>
+        <v>254.6175600000001</v>
       </c>
       <c r="G37">
         <v>21.8</v>
@@ -4321,28 +4321,28 @@
         <v>60.6</v>
       </c>
       <c r="M37">
-        <v>14.30809233</v>
+        <v>14.716894968</v>
       </c>
       <c r="N37">
-        <v>46.29190767</v>
+        <v>45.883105032</v>
       </c>
       <c r="O37">
-        <v>13.887572301</v>
+        <v>13.7649315096</v>
       </c>
       <c r="P37">
-        <v>32.404335369</v>
+        <v>32.1181735224</v>
       </c>
       <c r="Q37">
-        <v>35.704335369</v>
+        <v>35.4181735224</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1251451385468809</v>
+        <v>0.1261147893321955</v>
       </c>
       <c r="T37">
-        <v>0.7673281318408715</v>
+        <v>0.7767053960218877</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.235365456297695</v>
+        <v>4.11771641584498</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09527906517260511</v>
+        <v>0.09505279028973759</v>
       </c>
       <c r="C38">
-        <v>565.5166427735247</v>
+        <v>562.1116027097669</v>
       </c>
       <c r="D38">
-        <v>798.3342027735248</v>
+        <v>802.001872709767</v>
       </c>
       <c r="E38">
-        <v>254.54656</v>
+        <v>261.61927</v>
       </c>
       <c r="F38">
-        <v>254.61756</v>
+        <v>261.69027</v>
       </c>
       <c r="G38">
         <v>21.8</v>
@@ -4403,28 +4403,28 @@
         <v>60.6</v>
       </c>
       <c r="M38">
-        <v>14.716894968</v>
+        <v>15.125697606</v>
       </c>
       <c r="N38">
-        <v>45.883105032</v>
+        <v>45.474302394</v>
       </c>
       <c r="O38">
-        <v>13.7649315096</v>
+        <v>13.6422907182</v>
       </c>
       <c r="P38">
-        <v>32.1181735224</v>
+        <v>31.8320116758</v>
       </c>
       <c r="Q38">
-        <v>35.4181735224</v>
+        <v>35.13201167579999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1261147893321955</v>
+        <v>0.1271152226821232</v>
       </c>
       <c r="T38">
-        <v>0.7767053960218877</v>
+        <v>0.7863803511292853</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.117716415844981</v>
+        <v>4.006426782984306</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09505279028973759</v>
+        <v>0.09575751540687008</v>
       </c>
       <c r="C39">
-        <v>562.1116027097669</v>
+        <v>543.7254625064679</v>
       </c>
       <c r="D39">
-        <v>802.001872709767</v>
+        <v>790.6884425064679</v>
       </c>
       <c r="E39">
-        <v>261.61927</v>
+        <v>268.69198</v>
       </c>
       <c r="F39">
-        <v>261.69027</v>
+        <v>268.76298</v>
       </c>
       <c r="G39">
         <v>21.8</v>
@@ -4485,45 +4485,45 @@
         <v>60.6</v>
       </c>
       <c r="M39">
-        <v>15.125697606</v>
+        <v>16.475170674</v>
       </c>
       <c r="N39">
-        <v>45.474302394</v>
+        <v>44.124829326</v>
       </c>
       <c r="O39">
-        <v>13.6422907182</v>
+        <v>13.2374487978</v>
       </c>
       <c r="P39">
-        <v>31.8320116758</v>
+        <v>30.8873805282</v>
       </c>
       <c r="Q39">
-        <v>35.13201167579999</v>
+        <v>34.18738052819999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1271152226821232</v>
+        <v>0.1281479280755969</v>
       </c>
       <c r="T39">
-        <v>0.7863803511292853</v>
+        <v>0.7963674015627281</v>
       </c>
       <c r="U39">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>4.006426782984306</v>
+        <v>3.678262350000101</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09575751540687008</v>
+        <v>0.09555574052400258</v>
       </c>
       <c r="C40">
-        <v>543.7254625064679</v>
+        <v>539.8592381539775</v>
       </c>
       <c r="D40">
-        <v>790.6884425064679</v>
+        <v>793.8949281539776</v>
       </c>
       <c r="E40">
-        <v>268.69198</v>
+        <v>275.76469</v>
       </c>
       <c r="F40">
-        <v>268.76298</v>
+        <v>275.8356900000001</v>
       </c>
       <c r="G40">
         <v>21.8</v>
@@ -4567,28 +4567,28 @@
         <v>60.6</v>
       </c>
       <c r="M40">
-        <v>16.475170674</v>
+        <v>16.908727797</v>
       </c>
       <c r="N40">
-        <v>44.124829326</v>
+        <v>43.691272203</v>
       </c>
       <c r="O40">
-        <v>13.2374487978</v>
+        <v>13.1073816609</v>
       </c>
       <c r="P40">
-        <v>30.8873805282</v>
+        <v>30.5838905421</v>
       </c>
       <c r="Q40">
-        <v>34.18738052819999</v>
+        <v>33.8838905421</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1281479280755969</v>
+        <v>0.1292144926622993</v>
       </c>
       <c r="T40">
-        <v>0.7963674015627281</v>
+        <v>0.8066818962726773</v>
       </c>
       <c r="U40">
         <v>0.0613</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.678262350000101</v>
+        <v>3.583947930769329</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09555574052400258</v>
+        <v>0.09613796564113508</v>
       </c>
       <c r="C41">
-        <v>539.8592381539775</v>
+        <v>523.604083817021</v>
       </c>
       <c r="D41">
-        <v>793.8949281539776</v>
+        <v>784.7124838170211</v>
       </c>
       <c r="E41">
-        <v>275.76469</v>
+        <v>282.8374</v>
       </c>
       <c r="F41">
-        <v>275.8356900000001</v>
+        <v>282.9084</v>
       </c>
       <c r="G41">
         <v>21.8</v>
@@ -4649,45 +4649,45 @@
         <v>60.6</v>
       </c>
       <c r="M41">
-        <v>16.908727797</v>
+        <v>18.13442844</v>
       </c>
       <c r="N41">
-        <v>43.691272203</v>
+        <v>42.46557156</v>
       </c>
       <c r="O41">
-        <v>13.1073816609</v>
+        <v>12.739671468</v>
       </c>
       <c r="P41">
-        <v>30.5838905421</v>
+        <v>29.725900092</v>
       </c>
       <c r="Q41">
-        <v>33.8838905421</v>
+        <v>33.025900092</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1292144926622993</v>
+        <v>0.1303166094018918</v>
       </c>
       <c r="T41">
-        <v>0.8066818962726773</v>
+        <v>0.8173402074729581</v>
       </c>
       <c r="U41">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>3.583947930769329</v>
+        <v>3.34170995245329</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09613796564113508</v>
+        <v>0.09595579075826757</v>
       </c>
       <c r="C42">
-        <v>523.604083817021</v>
+        <v>519.3815911630704</v>
       </c>
       <c r="D42">
-        <v>784.7124838170211</v>
+        <v>787.5627011630705</v>
       </c>
       <c r="E42">
-        <v>282.8374</v>
+        <v>289.91011</v>
       </c>
       <c r="F42">
-        <v>282.9084</v>
+        <v>289.9811100000001</v>
       </c>
       <c r="G42">
         <v>21.8</v>
@@ -4731,28 +4731,28 @@
         <v>60.6</v>
       </c>
       <c r="M42">
-        <v>18.13442844</v>
+        <v>18.58778915100001</v>
       </c>
       <c r="N42">
-        <v>42.46557156</v>
+        <v>42.012210849</v>
       </c>
       <c r="O42">
-        <v>12.739671468</v>
+        <v>12.6036632547</v>
       </c>
       <c r="P42">
-        <v>29.725900092</v>
+        <v>29.4085475943</v>
       </c>
       <c r="Q42">
-        <v>33.025900092</v>
+        <v>32.7085475943</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1303166094018918</v>
+        <v>0.131456086030962</v>
       </c>
       <c r="T42">
-        <v>0.8173402074729581</v>
+        <v>0.8283598173579941</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.34170995245329</v>
+        <v>3.260204831661746</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09595579075826757</v>
+        <v>0.09577361587540005</v>
       </c>
       <c r="C43">
-        <v>519.3815911630704</v>
+        <v>515.1798789950651</v>
       </c>
       <c r="D43">
-        <v>787.5627011630705</v>
+        <v>790.4336989950652</v>
       </c>
       <c r="E43">
-        <v>289.91011</v>
+        <v>296.98282</v>
       </c>
       <c r="F43">
-        <v>289.9811100000001</v>
+        <v>297.05382</v>
       </c>
       <c r="G43">
         <v>21.8</v>
@@ -4813,28 +4813,28 @@
         <v>60.6</v>
       </c>
       <c r="M43">
-        <v>18.58778915100001</v>
+        <v>19.041149862</v>
       </c>
       <c r="N43">
-        <v>42.012210849</v>
+        <v>41.558850138</v>
       </c>
       <c r="O43">
-        <v>12.6036632547</v>
+        <v>12.4676550414</v>
       </c>
       <c r="P43">
-        <v>29.4085475943</v>
+        <v>29.0911950966</v>
       </c>
       <c r="Q43">
-        <v>32.7085475943</v>
+        <v>32.39119509659999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.131456086030962</v>
+        <v>0.1326348549575863</v>
       </c>
       <c r="T43">
-        <v>0.8283598173579941</v>
+        <v>0.83975941379079</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.260204831661746</v>
+        <v>3.182580907098371</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09577361587540006</v>
+        <v>0.09559144099253256</v>
       </c>
       <c r="C44">
-        <v>515.1798789950649</v>
+        <v>510.9991754053746</v>
       </c>
       <c r="D44">
-        <v>790.433698995065</v>
+        <v>793.3257054053746</v>
       </c>
       <c r="E44">
-        <v>296.98282</v>
+        <v>304.05553</v>
       </c>
       <c r="F44">
-        <v>297.05382</v>
+        <v>304.12653</v>
       </c>
       <c r="G44">
         <v>21.8</v>
@@ -4895,28 +4895,28 @@
         <v>60.6</v>
       </c>
       <c r="M44">
-        <v>19.041149862</v>
+        <v>19.494510573</v>
       </c>
       <c r="N44">
-        <v>41.558850138</v>
+        <v>41.10548942699999</v>
       </c>
       <c r="O44">
-        <v>12.4676550414</v>
+        <v>12.3316468281</v>
       </c>
       <c r="P44">
-        <v>29.0911950966</v>
+        <v>28.7738425989</v>
       </c>
       <c r="Q44">
-        <v>32.39119509659999</v>
+        <v>32.07384259889999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1326348549575863</v>
+        <v>0.1338549841974255</v>
       </c>
       <c r="T44">
-        <v>0.8397594137907899</v>
+        <v>0.8515589960633331</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.182580907098371</v>
+        <v>3.108567397630968</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09559144099253256</v>
+        <v>0.09540926610966505</v>
       </c>
       <c r="C45">
-        <v>510.9991754053746</v>
+        <v>506.8397118367675</v>
       </c>
       <c r="D45">
-        <v>793.3257054053746</v>
+        <v>796.2389518367676</v>
       </c>
       <c r="E45">
-        <v>304.05553</v>
+        <v>311.12824</v>
       </c>
       <c r="F45">
-        <v>304.12653</v>
+        <v>311.19924</v>
       </c>
       <c r="G45">
         <v>21.8</v>
@@ -4977,28 +4977,28 @@
         <v>60.6</v>
       </c>
       <c r="M45">
-        <v>19.494510573</v>
+        <v>19.947871284</v>
       </c>
       <c r="N45">
-        <v>41.10548942699999</v>
+        <v>40.65212871599999</v>
       </c>
       <c r="O45">
-        <v>12.3316468281</v>
+        <v>12.1956386148</v>
       </c>
       <c r="P45">
-        <v>28.7738425989</v>
+        <v>28.4564901012</v>
       </c>
       <c r="Q45">
-        <v>32.07384259889999</v>
+        <v>31.75649010119999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1338549841974255</v>
+        <v>0.1351186894815447</v>
       </c>
       <c r="T45">
-        <v>0.8515589960633331</v>
+        <v>0.8637799919884669</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.108567397630968</v>
+        <v>3.0379181385939</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09540926610966505</v>
+        <v>0.09768409122679755</v>
       </c>
       <c r="C46">
-        <v>506.8397118367675</v>
+        <v>464.8564093208477</v>
       </c>
       <c r="D46">
-        <v>796.2389518367676</v>
+        <v>761.3283593208478</v>
       </c>
       <c r="E46">
-        <v>311.12824</v>
+        <v>318.20095</v>
       </c>
       <c r="F46">
-        <v>311.19924</v>
+        <v>318.2719500000001</v>
       </c>
       <c r="G46">
         <v>21.8</v>
@@ -5059,45 +5059,45 @@
         <v>60.6</v>
       </c>
       <c r="M46">
-        <v>19.947871284</v>
+        <v>22.883753205</v>
       </c>
       <c r="N46">
-        <v>40.65212871599999</v>
+        <v>37.716246795</v>
       </c>
       <c r="O46">
-        <v>12.1956386148</v>
+        <v>11.3148740385</v>
       </c>
       <c r="P46">
-        <v>28.4564901012</v>
+        <v>26.4013727565</v>
       </c>
       <c r="Q46">
-        <v>31.75649010119999</v>
+        <v>29.70137275649999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1351186894815447</v>
+        <v>0.1364283476850864</v>
       </c>
       <c r="T46">
-        <v>0.8637799919884669</v>
+        <v>0.876445387765424</v>
       </c>
       <c r="U46">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V46">
         <v>0.3</v>
       </c>
       <c r="W46">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.0379181385939</v>
+        <v>2.648166996782641</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09768409122679755</v>
+        <v>0.09755651634393005</v>
       </c>
       <c r="C47">
-        <v>464.8564093208477</v>
+        <v>459.6603012083984</v>
       </c>
       <c r="D47">
-        <v>761.3283593208478</v>
+        <v>763.2049612083985</v>
       </c>
       <c r="E47">
-        <v>318.20095</v>
+        <v>325.27366</v>
       </c>
       <c r="F47">
-        <v>318.2719500000001</v>
+        <v>325.34466</v>
       </c>
       <c r="G47">
         <v>21.8</v>
@@ -5141,28 +5141,28 @@
         <v>60.6</v>
       </c>
       <c r="M47">
-        <v>22.883753205</v>
+        <v>23.39228105400001</v>
       </c>
       <c r="N47">
-        <v>37.716246795</v>
+        <v>37.207718946</v>
       </c>
       <c r="O47">
-        <v>11.3148740385</v>
+        <v>11.1623156838</v>
       </c>
       <c r="P47">
-        <v>26.4013727565</v>
+        <v>26.0454032622</v>
       </c>
       <c r="Q47">
-        <v>29.70137275649999</v>
+        <v>29.3454032622</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1364283476850864</v>
+        <v>0.1377865117480186</v>
       </c>
       <c r="T47">
-        <v>0.876445387765424</v>
+        <v>0.8895798722748608</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.648166996782641</v>
+        <v>2.590598149026497</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09755651634393005</v>
+        <v>0.09742894146106253</v>
       </c>
       <c r="C48">
-        <v>459.6603012083984</v>
+        <v>454.4734672456498</v>
       </c>
       <c r="D48">
-        <v>763.2049612083985</v>
+        <v>765.0908372456499</v>
       </c>
       <c r="E48">
-        <v>325.27366</v>
+        <v>332.34637</v>
       </c>
       <c r="F48">
-        <v>325.34466</v>
+        <v>332.4173700000001</v>
       </c>
       <c r="G48">
         <v>21.8</v>
@@ -5223,28 +5223,28 @@
         <v>60.6</v>
       </c>
       <c r="M48">
-        <v>23.39228105400001</v>
+        <v>23.90080890300001</v>
       </c>
       <c r="N48">
-        <v>37.207718946</v>
+        <v>36.699191097</v>
       </c>
       <c r="O48">
-        <v>11.1623156838</v>
+        <v>11.0097573291</v>
       </c>
       <c r="P48">
-        <v>26.0454032622</v>
+        <v>25.6894337679</v>
       </c>
       <c r="Q48">
-        <v>29.3454032622</v>
+        <v>28.9894337679</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1377865117480186</v>
+        <v>0.1391959272850236</v>
       </c>
       <c r="T48">
-        <v>0.8895798722748608</v>
+        <v>0.9032099977091822</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.590598149026497</v>
+        <v>2.535479039472742</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09742894146106253</v>
+        <v>0.09861176657819502</v>
       </c>
       <c r="C49">
-        <v>454.4734672456498</v>
+        <v>430.2650180379459</v>
       </c>
       <c r="D49">
-        <v>765.0908372456499</v>
+        <v>747.955098037946</v>
       </c>
       <c r="E49">
-        <v>332.34637</v>
+        <v>339.41908</v>
       </c>
       <c r="F49">
-        <v>332.4173700000001</v>
+        <v>339.49008</v>
       </c>
       <c r="G49">
         <v>21.8</v>
@@ -5305,45 +5305,45 @@
         <v>60.6</v>
       </c>
       <c r="M49">
-        <v>23.90080890300001</v>
+        <v>25.733348064</v>
       </c>
       <c r="N49">
-        <v>36.699191097</v>
+        <v>34.866651936</v>
       </c>
       <c r="O49">
-        <v>11.0097573291</v>
+        <v>10.4599955808</v>
       </c>
       <c r="P49">
-        <v>25.6894337679</v>
+        <v>24.4066563552</v>
       </c>
       <c r="Q49">
-        <v>28.9894337679</v>
+        <v>27.7066563552</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1391959272850236</v>
+        <v>0.1406595511119135</v>
       </c>
       <c r="T49">
-        <v>0.9032099977091822</v>
+        <v>0.9173643587371312</v>
       </c>
       <c r="U49">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V49">
         <v>0.3</v>
       </c>
       <c r="W49">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>2.535479039472742</v>
+        <v>2.354920931753033</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09861176657819502</v>
+        <v>0.09851149169532752</v>
       </c>
       <c r="C50">
-        <v>430.2650180379459</v>
+        <v>424.6151687355602</v>
       </c>
       <c r="D50">
-        <v>747.955098037946</v>
+        <v>749.3779587355602</v>
       </c>
       <c r="E50">
-        <v>339.41908</v>
+        <v>346.49179</v>
       </c>
       <c r="F50">
-        <v>339.49008</v>
+        <v>346.56279</v>
       </c>
       <c r="G50">
         <v>21.8</v>
@@ -5387,28 +5387,28 @@
         <v>60.6</v>
       </c>
       <c r="M50">
-        <v>25.733348064</v>
+        <v>26.269459482</v>
       </c>
       <c r="N50">
-        <v>34.866651936</v>
+        <v>34.330540518</v>
       </c>
       <c r="O50">
-        <v>10.4599955808</v>
+        <v>10.2991621554</v>
       </c>
       <c r="P50">
-        <v>24.4066563552</v>
+        <v>24.0313783626</v>
       </c>
       <c r="Q50">
-        <v>27.7066563552</v>
+        <v>27.3313783626</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1406595511119135</v>
+        <v>0.1421805719516226</v>
       </c>
       <c r="T50">
-        <v>0.9173643587371312</v>
+        <v>0.9320737927465684</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.354920931753033</v>
+        <v>2.30686132090093</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09851149169532752</v>
+        <v>0.09841121681246001</v>
       </c>
       <c r="C51">
-        <v>424.6151687355602</v>
+        <v>418.9707432647618</v>
       </c>
       <c r="D51">
-        <v>749.3779587355602</v>
+        <v>750.8062432647619</v>
       </c>
       <c r="E51">
-        <v>346.49179</v>
+        <v>353.5645</v>
       </c>
       <c r="F51">
-        <v>346.56279</v>
+        <v>353.6355</v>
       </c>
       <c r="G51">
         <v>21.8</v>
@@ -5469,28 +5469,28 @@
         <v>60.6</v>
       </c>
       <c r="M51">
-        <v>26.269459482</v>
+        <v>26.80557090000001</v>
       </c>
       <c r="N51">
-        <v>34.330540518</v>
+        <v>33.7944291</v>
       </c>
       <c r="O51">
-        <v>10.2991621554</v>
+        <v>10.13832873</v>
       </c>
       <c r="P51">
-        <v>24.0313783626</v>
+        <v>23.65610037</v>
       </c>
       <c r="Q51">
-        <v>27.3313783626</v>
+        <v>26.95610036999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1421805719516226</v>
+        <v>0.14376243362492</v>
       </c>
       <c r="T51">
-        <v>0.9320737927465684</v>
+        <v>0.9473716041163832</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.30686132090093</v>
+        <v>2.260724094482912</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09841121681246001</v>
+        <v>0.09831094192959253</v>
       </c>
       <c r="C52">
-        <v>418.9707432647618</v>
+        <v>413.3317726975926</v>
       </c>
       <c r="D52">
-        <v>750.8062432647619</v>
+        <v>752.2399826975927</v>
       </c>
       <c r="E52">
-        <v>353.5645</v>
+        <v>360.63721</v>
       </c>
       <c r="F52">
-        <v>353.6355</v>
+        <v>360.7082100000001</v>
       </c>
       <c r="G52">
         <v>21.8</v>
@@ -5551,28 +5551,28 @@
         <v>60.6</v>
       </c>
       <c r="M52">
-        <v>26.80557090000001</v>
+        <v>27.34168231800001</v>
       </c>
       <c r="N52">
-        <v>33.7944291</v>
+        <v>33.258317682</v>
       </c>
       <c r="O52">
-        <v>10.13832873</v>
+        <v>9.9774953046</v>
       </c>
       <c r="P52">
-        <v>23.65610037</v>
+        <v>23.2808223774</v>
       </c>
       <c r="Q52">
-        <v>26.95610036999999</v>
+        <v>26.5808223774</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.14376243362492</v>
+        <v>0.1454088610808011</v>
       </c>
       <c r="T52">
-        <v>0.9473716041163832</v>
+        <v>0.9632938159502721</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.260724094482912</v>
+        <v>2.216396171061678</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09831094192959253</v>
+        <v>0.09821066704672499</v>
       </c>
       <c r="C53">
-        <v>413.3317726975926</v>
+        <v>407.6982883438916</v>
       </c>
       <c r="D53">
-        <v>752.2399826975927</v>
+        <v>753.6792083438917</v>
       </c>
       <c r="E53">
-        <v>360.63721</v>
+        <v>367.70992</v>
       </c>
       <c r="F53">
-        <v>360.7082100000001</v>
+        <v>367.78092</v>
       </c>
       <c r="G53">
         <v>21.8</v>
@@ -5633,28 +5633,28 @@
         <v>60.6</v>
       </c>
       <c r="M53">
-        <v>27.34168231800001</v>
+        <v>27.877793736</v>
       </c>
       <c r="N53">
-        <v>33.258317682</v>
+        <v>32.72220626399999</v>
       </c>
       <c r="O53">
-        <v>9.9774953046</v>
+        <v>9.816661879199998</v>
       </c>
       <c r="P53">
-        <v>23.2808223774</v>
+        <v>22.9055443848</v>
       </c>
       <c r="Q53">
-        <v>26.5808223774</v>
+        <v>26.20554438479999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1454088610808011</v>
+        <v>0.1471238896806771</v>
       </c>
       <c r="T53">
-        <v>0.9632938159502721</v>
+        <v>0.9798794532772395</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.216396171061678</v>
+        <v>2.173773167772031</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09821066704672499</v>
+        <v>0.09811039216385749</v>
       </c>
       <c r="C54">
-        <v>407.6982883438916</v>
+        <v>402.0703217535686</v>
       </c>
       <c r="D54">
-        <v>753.6792083438917</v>
+        <v>755.1239517535687</v>
       </c>
       <c r="E54">
-        <v>367.70992</v>
+        <v>374.78263</v>
       </c>
       <c r="F54">
-        <v>367.78092</v>
+        <v>374.8536300000001</v>
       </c>
       <c r="G54">
         <v>21.8</v>
@@ -5715,28 +5715,28 @@
         <v>60.6</v>
       </c>
       <c r="M54">
-        <v>27.877793736</v>
+        <v>28.41390515400001</v>
       </c>
       <c r="N54">
-        <v>32.72220626399999</v>
+        <v>32.18609484599999</v>
       </c>
       <c r="O54">
-        <v>9.816661879199998</v>
+        <v>9.655828453799996</v>
       </c>
       <c r="P54">
-        <v>22.9055443848</v>
+        <v>22.53026639219999</v>
       </c>
       <c r="Q54">
-        <v>26.20554438479999</v>
+        <v>25.83026639219999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1471238896806771</v>
+        <v>0.1489118982209734</v>
       </c>
       <c r="T54">
-        <v>0.9798794532772395</v>
+        <v>0.9971708624053546</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.173773167772031</v>
+        <v>2.13275857970086</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09811039216385749</v>
+        <v>0.09801011728099</v>
       </c>
       <c r="C55">
-        <v>402.0703217535686</v>
+        <v>396.4479047189148</v>
       </c>
       <c r="D55">
-        <v>755.1239517535687</v>
+        <v>756.5742447189149</v>
       </c>
       <c r="E55">
-        <v>374.78263</v>
+        <v>381.85534</v>
       </c>
       <c r="F55">
-        <v>374.8536300000001</v>
+        <v>381.92634</v>
       </c>
       <c r="G55">
         <v>21.8</v>
@@ -5797,28 +5797,28 @@
         <v>60.6</v>
       </c>
       <c r="M55">
-        <v>28.41390515400001</v>
+        <v>28.95001657200001</v>
       </c>
       <c r="N55">
-        <v>32.18609484599999</v>
+        <v>31.649983428</v>
       </c>
       <c r="O55">
-        <v>9.655828453799996</v>
+        <v>9.494995028399998</v>
       </c>
       <c r="P55">
-        <v>22.53026639219999</v>
+        <v>22.1549883996</v>
       </c>
       <c r="Q55">
-        <v>25.83026639219999</v>
+        <v>25.45498839959999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1489118982209734</v>
+        <v>0.1507776462630217</v>
       </c>
       <c r="T55">
-        <v>0.9971708624053546</v>
+        <v>1.015214071930344</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.13275857970086</v>
+        <v>2.093263050447141</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09801011728099</v>
+        <v>0.09790984239812249</v>
       </c>
       <c r="C56">
-        <v>396.4479047189148</v>
+        <v>390.831069276933</v>
       </c>
       <c r="D56">
-        <v>756.5742447189149</v>
+        <v>758.0301192769331</v>
       </c>
       <c r="E56">
-        <v>381.85534</v>
+        <v>388.92805</v>
       </c>
       <c r="F56">
-        <v>381.92634</v>
+        <v>388.9990500000001</v>
       </c>
       <c r="G56">
         <v>21.8</v>
@@ -5879,28 +5879,28 @@
         <v>60.6</v>
       </c>
       <c r="M56">
-        <v>28.95001657200001</v>
+        <v>29.48612799000001</v>
       </c>
       <c r="N56">
-        <v>31.649983428</v>
+        <v>31.11387200999999</v>
       </c>
       <c r="O56">
-        <v>9.494995028399998</v>
+        <v>9.334161602999998</v>
       </c>
       <c r="P56">
-        <v>22.1549883996</v>
+        <v>21.779710407</v>
       </c>
       <c r="Q56">
-        <v>25.45498839959999</v>
+        <v>25.07971040699999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1507776462630217</v>
+        <v>0.1527263164402722</v>
       </c>
       <c r="T56">
-        <v>1.015214071930344</v>
+        <v>1.034059201878667</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.093263050447141</v>
+        <v>2.055203722257192</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09790984239812249</v>
+        <v>0.09780956751525498</v>
       </c>
       <c r="C57">
-        <v>390.831069276933</v>
+        <v>385.2198477116954</v>
       </c>
       <c r="D57">
-        <v>758.0301192769331</v>
+        <v>759.4916077116956</v>
       </c>
       <c r="E57">
-        <v>388.92805</v>
+        <v>396.0007600000001</v>
       </c>
       <c r="F57">
-        <v>388.9990500000001</v>
+        <v>396.0717600000001</v>
       </c>
       <c r="G57">
         <v>21.8</v>
@@ -5961,28 +5961,28 @@
         <v>60.6</v>
       </c>
       <c r="M57">
-        <v>29.48612799000001</v>
+        <v>30.02223940800001</v>
       </c>
       <c r="N57">
-        <v>31.11387200999999</v>
+        <v>30.57776059199999</v>
       </c>
       <c r="O57">
-        <v>9.334161602999998</v>
+        <v>9.173328177599997</v>
       </c>
       <c r="P57">
-        <v>21.779710407</v>
+        <v>21.40443241439999</v>
       </c>
       <c r="Q57">
-        <v>25.07971040699999</v>
+        <v>24.70443241439999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1527263164402722</v>
+        <v>0.1547635625346704</v>
       </c>
       <c r="T57">
-        <v>1.034059201878667</v>
+        <v>1.053760928642822</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.055203722257192</v>
+        <v>2.018503655788313</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09780956751525498</v>
+        <v>0.1033750926323875</v>
       </c>
       <c r="C58">
-        <v>385.2198477116954</v>
+        <v>304.7305017027937</v>
       </c>
       <c r="D58">
-        <v>759.4916077116956</v>
+        <v>686.0749717027938</v>
       </c>
       <c r="E58">
-        <v>396.0007600000001</v>
+        <v>403.07347</v>
       </c>
       <c r="F58">
-        <v>396.0717600000001</v>
+        <v>403.1444700000001</v>
       </c>
       <c r="G58">
         <v>21.8</v>
@@ -6043,45 +6043,45 @@
         <v>60.6</v>
       </c>
       <c r="M58">
-        <v>30.02223940800001</v>
+        <v>36.28300230000001</v>
       </c>
       <c r="N58">
-        <v>30.57776059199999</v>
+        <v>24.31699769999999</v>
       </c>
       <c r="O58">
-        <v>9.173328177599997</v>
+        <v>7.295099309999998</v>
       </c>
       <c r="P58">
-        <v>21.40443241439999</v>
+        <v>17.02189839</v>
       </c>
       <c r="Q58">
-        <v>24.70443241439999</v>
+        <v>20.32189838999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1547635625346704</v>
+        <v>0.1568955642613662</v>
       </c>
       <c r="T58">
-        <v>1.053760928642822</v>
+        <v>1.074379014791357</v>
       </c>
       <c r="U58">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V58">
         <v>0.3</v>
       </c>
       <c r="W58">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.018503655788313</v>
+        <v>1.670203570777824</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1033750926323875</v>
+        <v>0.10337421774952</v>
       </c>
       <c r="C59">
-        <v>304.7305017027937</v>
+        <v>297.668217119969</v>
       </c>
       <c r="D59">
-        <v>686.0749717027938</v>
+        <v>686.0853971199691</v>
       </c>
       <c r="E59">
-        <v>403.07347</v>
+        <v>410.1461800000001</v>
       </c>
       <c r="F59">
-        <v>403.1444700000001</v>
+        <v>410.2171800000001</v>
       </c>
       <c r="G59">
         <v>21.8</v>
@@ -6125,28 +6125,28 @@
         <v>60.6</v>
       </c>
       <c r="M59">
-        <v>36.28300230000001</v>
+        <v>36.91954620000001</v>
       </c>
       <c r="N59">
-        <v>24.31699769999999</v>
+        <v>23.6804538</v>
       </c>
       <c r="O59">
-        <v>7.295099309999998</v>
+        <v>7.104136139999999</v>
       </c>
       <c r="P59">
-        <v>17.02189839</v>
+        <v>16.57631766</v>
       </c>
       <c r="Q59">
-        <v>20.32189838999999</v>
+        <v>19.87631765999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1568955642613662</v>
+        <v>0.1591290898798094</v>
       </c>
       <c r="T59">
-        <v>1.074379014791357</v>
+        <v>1.095978914566012</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.670203570777824</v>
+        <v>1.641406957488551</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.10337421774952</v>
+        <v>0.1033733428666525</v>
       </c>
       <c r="C60">
-        <v>297.668217119969</v>
+        <v>290.6059328539928</v>
       </c>
       <c r="D60">
-        <v>686.0853971199691</v>
+        <v>686.0958228539929</v>
       </c>
       <c r="E60">
-        <v>410.14618</v>
+        <v>417.21889</v>
       </c>
       <c r="F60">
-        <v>410.21718</v>
+        <v>417.28989</v>
       </c>
       <c r="G60">
         <v>21.8</v>
@@ -6207,28 +6207,28 @@
         <v>60.6</v>
       </c>
       <c r="M60">
-        <v>36.9195462</v>
+        <v>37.5560901</v>
       </c>
       <c r="N60">
-        <v>23.6804538</v>
+        <v>23.0439099</v>
       </c>
       <c r="O60">
-        <v>7.10413614</v>
+        <v>6.913172970000001</v>
       </c>
       <c r="P60">
-        <v>16.57631766</v>
+        <v>16.13073693</v>
       </c>
       <c r="Q60">
-        <v>19.87631766</v>
+        <v>19.43073693</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1591290898798094</v>
+        <v>0.161471567967445</v>
       </c>
       <c r="T60">
-        <v>1.095978914566012</v>
+        <v>1.118632467988211</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.641406957488551</v>
+        <v>1.613586500581966</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1033733428666525</v>
+        <v>0.103372467983785</v>
       </c>
       <c r="C61">
-        <v>290.6059328539928</v>
+        <v>283.5436489048795</v>
       </c>
       <c r="D61">
-        <v>686.0958228539929</v>
+        <v>686.1062489048796</v>
       </c>
       <c r="E61">
-        <v>417.21889</v>
+        <v>424.2916</v>
       </c>
       <c r="F61">
-        <v>417.28989</v>
+        <v>424.3626</v>
       </c>
       <c r="G61">
         <v>21.8</v>
@@ -6289,28 +6289,28 @@
         <v>60.6</v>
       </c>
       <c r="M61">
-        <v>37.5560901</v>
+        <v>38.19263400000001</v>
       </c>
       <c r="N61">
-        <v>23.0439099</v>
+        <v>22.407366</v>
       </c>
       <c r="O61">
-        <v>6.913172970000001</v>
+        <v>6.722209799999999</v>
       </c>
       <c r="P61">
-        <v>16.13073693</v>
+        <v>15.6851562</v>
       </c>
       <c r="Q61">
-        <v>19.43073693</v>
+        <v>18.9851562</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.161471567967445</v>
+        <v>0.1639311699594624</v>
       </c>
       <c r="T61">
-        <v>1.118632467988211</v>
+        <v>1.142418699081521</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.613586500581966</v>
+        <v>1.586693392238933</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.103372467983785</v>
+        <v>0.1033715931009175</v>
       </c>
       <c r="C62">
-        <v>283.5436489048795</v>
+        <v>276.481365272644</v>
       </c>
       <c r="D62">
-        <v>686.1062489048796</v>
+        <v>686.1166752726441</v>
       </c>
       <c r="E62">
-        <v>424.2916</v>
+        <v>431.36431</v>
       </c>
       <c r="F62">
-        <v>424.3626</v>
+        <v>431.43531</v>
       </c>
       <c r="G62">
         <v>21.8</v>
@@ -6371,28 +6371,28 @@
         <v>60.6</v>
       </c>
       <c r="M62">
-        <v>38.19263400000001</v>
+        <v>38.8291779</v>
       </c>
       <c r="N62">
-        <v>22.407366</v>
+        <v>21.7708221</v>
       </c>
       <c r="O62">
-        <v>6.722209799999999</v>
+        <v>6.531246630000001</v>
       </c>
       <c r="P62">
-        <v>15.6851562</v>
+        <v>15.23957547</v>
       </c>
       <c r="Q62">
-        <v>18.9851562</v>
+        <v>18.53957547</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1639311699594624</v>
+        <v>0.1665169053869678</v>
       </c>
       <c r="T62">
-        <v>1.142418699081521</v>
+        <v>1.167424736897564</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.586693392238933</v>
+        <v>1.560682025153049</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1033715931009175</v>
+        <v>0.1033707182180499</v>
       </c>
       <c r="C63">
-        <v>276.481365272644</v>
+        <v>269.4190819573005</v>
       </c>
       <c r="D63">
-        <v>686.1166752726441</v>
+        <v>686.1271019573006</v>
       </c>
       <c r="E63">
-        <v>431.36431</v>
+        <v>438.43702</v>
       </c>
       <c r="F63">
-        <v>431.43531</v>
+        <v>438.50802</v>
       </c>
       <c r="G63">
         <v>21.8</v>
@@ -6453,28 +6453,28 @@
         <v>60.6</v>
       </c>
       <c r="M63">
-        <v>38.8291779</v>
+        <v>39.4657218</v>
       </c>
       <c r="N63">
-        <v>21.7708221</v>
+        <v>21.1342782</v>
       </c>
       <c r="O63">
-        <v>6.531246630000001</v>
+        <v>6.340283459999999</v>
       </c>
       <c r="P63">
-        <v>15.23957547</v>
+        <v>14.79399474</v>
       </c>
       <c r="Q63">
-        <v>18.53957547</v>
+        <v>18.09399474</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1665169053869678</v>
+        <v>0.169238732152763</v>
       </c>
       <c r="T63">
-        <v>1.167424736897564</v>
+        <v>1.193746881967083</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.560682025153049</v>
+        <v>1.535509734424774</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1033707182180499</v>
+        <v>0.1033698433351824</v>
       </c>
       <c r="C64">
-        <v>269.4190819573005</v>
+        <v>262.3567989588633</v>
       </c>
       <c r="D64">
-        <v>686.1271019573006</v>
+        <v>686.1375289588634</v>
       </c>
       <c r="E64">
-        <v>438.43702</v>
+        <v>445.50973</v>
       </c>
       <c r="F64">
-        <v>438.50802</v>
+        <v>445.5807300000001</v>
       </c>
       <c r="G64">
         <v>21.8</v>
@@ -6535,28 +6535,28 @@
         <v>60.6</v>
       </c>
       <c r="M64">
-        <v>39.4657218</v>
+        <v>40.1022657</v>
       </c>
       <c r="N64">
-        <v>21.1342782</v>
+        <v>20.4977343</v>
       </c>
       <c r="O64">
-        <v>6.340283459999999</v>
+        <v>6.149320289999999</v>
       </c>
       <c r="P64">
-        <v>14.79399474</v>
+        <v>14.34841401</v>
       </c>
       <c r="Q64">
-        <v>18.09399474</v>
+        <v>17.64841401</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.169238732152763</v>
+        <v>0.1721076846896823</v>
       </c>
       <c r="T64">
-        <v>1.193746881967083</v>
+        <v>1.221491845689009</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.535509734424774</v>
+        <v>1.511136564037079</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1033698433351824</v>
+        <v>0.1322704943136781</v>
       </c>
       <c r="C65">
-        <v>262.3567989588633</v>
+        <v>25.95937646498726</v>
       </c>
       <c r="D65">
-        <v>686.1375289588634</v>
+        <v>456.8128164649873</v>
       </c>
       <c r="E65">
-        <v>445.50973</v>
+        <v>452.58244</v>
       </c>
       <c r="F65">
-        <v>445.5807300000001</v>
+        <v>452.65344</v>
       </c>
       <c r="G65">
         <v>21.8</v>
@@ -6617,45 +6617,45 @@
         <v>60.6</v>
       </c>
       <c r="M65">
-        <v>40.1022657</v>
+        <v>66.44952499200001</v>
       </c>
       <c r="N65">
-        <v>20.4977343</v>
+        <v>-5.849524992000006</v>
       </c>
       <c r="O65">
-        <v>6.149320289999999</v>
+        <v>-1.754857497600002</v>
       </c>
       <c r="P65">
-        <v>14.34841401</v>
+        <v>-4.094667494400005</v>
       </c>
       <c r="Q65">
-        <v>17.64841401</v>
+        <v>-0.7946674944000076</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1721076846896823</v>
+        <v>0.1778414646331912</v>
       </c>
       <c r="T65">
-        <v>1.221491845689009</v>
+        <v>1.276941879969809</v>
       </c>
       <c r="U65">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.3</v>
+        <v>0.273591120511226</v>
       </c>
       <c r="W65">
-        <v>0.063</v>
+        <v>0.106636823508952</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y65">
-        <v>1.511136564037079</v>
+        <v>0.9119704017040868</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1322704943136781</v>
+        <v>0.1332804943136781</v>
       </c>
       <c r="C66">
-        <v>25.95937646498726</v>
+        <v>13.61256566972583</v>
       </c>
       <c r="D66">
-        <v>456.8128164649873</v>
+        <v>451.5387156697259</v>
       </c>
       <c r="E66">
-        <v>452.58244</v>
+        <v>459.65515</v>
       </c>
       <c r="F66">
-        <v>452.65344</v>
+        <v>459.7261500000001</v>
       </c>
       <c r="G66">
         <v>21.8</v>
@@ -6699,37 +6699,37 @@
         <v>60.6</v>
       </c>
       <c r="M66">
-        <v>66.44952499200001</v>
+        <v>67.48779882000002</v>
       </c>
       <c r="N66">
-        <v>-5.849524992000006</v>
+        <v>-6.887798820000022</v>
       </c>
       <c r="O66">
-        <v>-1.754857497600002</v>
+        <v>-2.066339646000007</v>
       </c>
       <c r="P66">
-        <v>-4.094667494400005</v>
+        <v>-4.821459174000015</v>
       </c>
       <c r="Q66">
-        <v>-0.7946674944000076</v>
+        <v>-1.521459174000018</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1778414646331912</v>
+        <v>0.1816140779084252</v>
       </c>
       <c r="T66">
-        <v>1.276941879969809</v>
+        <v>1.313425933683232</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.273591120511226</v>
+        <v>0.2693820263495148</v>
       </c>
       <c r="W66">
-        <v>0.106636823508952</v>
+        <v>0.1072547185318912</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.9119704017040868</v>
+        <v>0.897940087831716</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1332804943136781</v>
+        <v>0.1342904943136781</v>
       </c>
       <c r="C67">
-        <v>13.61256566972583</v>
+        <v>1.386148411522242</v>
       </c>
       <c r="D67">
-        <v>451.5387156697259</v>
+        <v>446.3850084115223</v>
       </c>
       <c r="E67">
-        <v>459.65515</v>
+        <v>466.72786</v>
       </c>
       <c r="F67">
-        <v>459.7261500000001</v>
+        <v>466.79886</v>
       </c>
       <c r="G67">
         <v>21.8</v>
@@ -6781,37 +6781,37 @@
         <v>60.6</v>
       </c>
       <c r="M67">
-        <v>67.48779882000002</v>
+        <v>68.52607264800001</v>
       </c>
       <c r="N67">
-        <v>-6.887798820000022</v>
+        <v>-7.926072648000009</v>
       </c>
       <c r="O67">
-        <v>-2.066339646000007</v>
+        <v>-2.377821794400003</v>
       </c>
       <c r="P67">
-        <v>-4.821459174000015</v>
+        <v>-5.548250853600006</v>
       </c>
       <c r="Q67">
-        <v>-1.521459174000018</v>
+        <v>-2.248250853600009</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1816140779084252</v>
+        <v>0.1856086096116142</v>
       </c>
       <c r="T67">
-        <v>1.313425933683232</v>
+        <v>1.352056108203327</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2693820263495148</v>
+        <v>0.2653004804957343</v>
       </c>
       <c r="W67">
-        <v>0.1072547185318912</v>
+        <v>0.1078538894632262</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.897940087831716</v>
+        <v>0.8843349349857811</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1342904943136781</v>
+        <v>0.1353004943136781</v>
       </c>
       <c r="C68">
-        <v>1.386148411522242</v>
+        <v>-10.72395118004277</v>
       </c>
       <c r="D68">
-        <v>446.3850084115223</v>
+        <v>441.3476188199573</v>
       </c>
       <c r="E68">
-        <v>466.72786</v>
+        <v>473.8005700000001</v>
       </c>
       <c r="F68">
-        <v>466.79886</v>
+        <v>473.8715700000001</v>
       </c>
       <c r="G68">
         <v>21.8</v>
@@ -6863,37 +6863,37 @@
         <v>60.6</v>
       </c>
       <c r="M68">
-        <v>68.52607264800001</v>
+        <v>69.56434647600001</v>
       </c>
       <c r="N68">
-        <v>-7.926072648000009</v>
+        <v>-8.96434647600001</v>
       </c>
       <c r="O68">
-        <v>-2.377821794400003</v>
+        <v>-2.689303942800003</v>
       </c>
       <c r="P68">
-        <v>-5.548250853600006</v>
+        <v>-6.275042533200008</v>
       </c>
       <c r="Q68">
-        <v>-2.248250853600009</v>
+        <v>-2.975042533200011</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1856086096116142</v>
+        <v>0.1898452341452995</v>
       </c>
       <c r="T68">
-        <v>1.352056108203327</v>
+        <v>1.39302750542161</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2653004804957343</v>
+        <v>0.2613407718316189</v>
       </c>
       <c r="W68">
-        <v>0.1078538894632262</v>
+        <v>0.1084351746951184</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8843349349857811</v>
+        <v>0.8711359061053963</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1353004943136781</v>
+        <v>0.1363104943136781</v>
       </c>
       <c r="C69">
-        <v>-10.72395118004277</v>
+        <v>-22.7216270460263</v>
       </c>
       <c r="D69">
-        <v>441.3476188199573</v>
+        <v>436.4226529539738</v>
       </c>
       <c r="E69">
-        <v>473.8005700000001</v>
+        <v>480.8732800000001</v>
       </c>
       <c r="F69">
-        <v>473.8715700000001</v>
+        <v>480.9442800000001</v>
       </c>
       <c r="G69">
         <v>21.8</v>
@@ -6945,37 +6945,37 @@
         <v>60.6</v>
       </c>
       <c r="M69">
-        <v>69.56434647600001</v>
+        <v>70.60262030400003</v>
       </c>
       <c r="N69">
-        <v>-8.96434647600001</v>
+        <v>-10.00262030400003</v>
       </c>
       <c r="O69">
-        <v>-2.689303942800003</v>
+        <v>-3.000786091200008</v>
       </c>
       <c r="P69">
-        <v>-6.275042533200008</v>
+        <v>-7.001834212800018</v>
       </c>
       <c r="Q69">
-        <v>-2.975042533200011</v>
+        <v>-3.701834212800021</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1898452341452995</v>
+        <v>0.1943466477123401</v>
       </c>
       <c r="T69">
-        <v>1.39302750542161</v>
+        <v>1.436559614966035</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2613407718316189</v>
+        <v>0.2574975251870362</v>
       </c>
       <c r="W69">
-        <v>0.1084351746951184</v>
+        <v>0.1089993633025431</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8711359061053963</v>
+        <v>0.8583250839567873</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1363104943136781</v>
+        <v>0.1373204943136782</v>
       </c>
       <c r="C70">
-        <v>-22.7216270460263</v>
+        <v>-34.61060123678516</v>
       </c>
       <c r="D70">
-        <v>436.4226529539738</v>
+        <v>431.6063887632149</v>
       </c>
       <c r="E70">
-        <v>480.8732800000001</v>
+        <v>487.9459900000001</v>
       </c>
       <c r="F70">
-        <v>480.9442800000001</v>
+        <v>488.0169900000001</v>
       </c>
       <c r="G70">
         <v>21.8</v>
@@ -7027,37 +7027,37 @@
         <v>60.6</v>
       </c>
       <c r="M70">
-        <v>70.60262030400003</v>
+        <v>71.64089413200001</v>
       </c>
       <c r="N70">
-        <v>-10.00262030400003</v>
+        <v>-11.04089413200001</v>
       </c>
       <c r="O70">
-        <v>-3.000786091200008</v>
+        <v>-3.312268239600004</v>
       </c>
       <c r="P70">
-        <v>-7.001834212800018</v>
+        <v>-7.728625892400009</v>
       </c>
       <c r="Q70">
-        <v>-3.701834212800021</v>
+        <v>-4.428625892400012</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1943466477123401</v>
+        <v>0.1991384750578995</v>
       </c>
       <c r="T70">
-        <v>1.436559614966035</v>
+        <v>1.482900247706875</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2574975251870362</v>
+        <v>0.2537656769959198</v>
       </c>
       <c r="W70">
-        <v>0.1089993633025431</v>
+        <v>0.109547198616999</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8583250839567873</v>
+        <v>0.8458855899863993</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1373204943136782</v>
+        <v>0.1383304943136781</v>
       </c>
       <c r="C71">
-        <v>-34.61060123678516</v>
+        <v>-46.39443329318595</v>
       </c>
       <c r="D71">
-        <v>431.6063887632149</v>
+        <v>426.8952667068141</v>
       </c>
       <c r="E71">
-        <v>487.9459900000001</v>
+        <v>495.0187000000001</v>
       </c>
       <c r="F71">
-        <v>488.0169900000001</v>
+        <v>495.0897000000001</v>
       </c>
       <c r="G71">
         <v>21.8</v>
@@ -7109,37 +7109,37 @@
         <v>60.6</v>
       </c>
       <c r="M71">
-        <v>71.64089413200001</v>
+        <v>72.67916796000003</v>
       </c>
       <c r="N71">
-        <v>-11.04089413200001</v>
+        <v>-12.07916796000003</v>
       </c>
       <c r="O71">
-        <v>-3.312268239600004</v>
+        <v>-3.623750388000008</v>
       </c>
       <c r="P71">
-        <v>-7.728625892400009</v>
+        <v>-8.45541757200002</v>
       </c>
       <c r="Q71">
-        <v>-4.428625892400012</v>
+        <v>-5.155417572000022</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1991384750578995</v>
+        <v>0.2042497575598295</v>
       </c>
       <c r="T71">
-        <v>1.482900247706875</v>
+        <v>1.532330255963771</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2537656769959198</v>
+        <v>0.2501404530388351</v>
       </c>
       <c r="W71">
-        <v>0.109547198616999</v>
+        <v>0.110079381493899</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8458855899863993</v>
+        <v>0.8338015101294505</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1383304943136781</v>
+        <v>0.1393404943136781</v>
       </c>
       <c r="C72">
-        <v>-46.39443329318595</v>
+        <v>-58.0765290200564</v>
       </c>
       <c r="D72">
-        <v>426.8952667068141</v>
+        <v>422.2858809799437</v>
       </c>
       <c r="E72">
-        <v>495.0187000000001</v>
+        <v>502.0914100000001</v>
       </c>
       <c r="F72">
-        <v>495.0897000000001</v>
+        <v>502.1624100000001</v>
       </c>
       <c r="G72">
         <v>21.8</v>
@@ -7191,37 +7191,37 @@
         <v>60.6</v>
       </c>
       <c r="M72">
-        <v>72.67916796000003</v>
+        <v>73.71744178800002</v>
       </c>
       <c r="N72">
-        <v>-12.07916796000003</v>
+        <v>-13.11744178800001</v>
       </c>
       <c r="O72">
-        <v>-3.623750388000008</v>
+        <v>-3.935232536400004</v>
       </c>
       <c r="P72">
-        <v>-8.45541757200002</v>
+        <v>-9.18220925160001</v>
       </c>
       <c r="Q72">
-        <v>-5.155417572000022</v>
+        <v>-5.882209251600013</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2042497575598295</v>
+        <v>0.2097135423032719</v>
       </c>
       <c r="T72">
-        <v>1.532330255963771</v>
+        <v>1.585169230307349</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2501404530388351</v>
+        <v>0.2466173480664572</v>
       </c>
       <c r="W72">
-        <v>0.110079381493899</v>
+        <v>0.1105965733038441</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8338015101294505</v>
+        <v>0.8220578268881908</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1393404943136781</v>
+        <v>0.1403504943136782</v>
       </c>
       <c r="C73">
-        <v>-58.07652902005634</v>
+        <v>-69.6601486973214</v>
       </c>
       <c r="D73">
-        <v>422.2858809799437</v>
+        <v>417.7749713026786</v>
       </c>
       <c r="E73">
-        <v>502.09141</v>
+        <v>509.16412</v>
       </c>
       <c r="F73">
-        <v>502.16241</v>
+        <v>509.2351200000001</v>
       </c>
       <c r="G73">
         <v>21.8</v>
@@ -7273,37 +7273,37 @@
         <v>60.6</v>
       </c>
       <c r="M73">
-        <v>73.71744178800002</v>
+        <v>74.75571561600002</v>
       </c>
       <c r="N73">
-        <v>-13.11744178800001</v>
+        <v>-14.15571561600002</v>
       </c>
       <c r="O73">
-        <v>-3.935232536400004</v>
+        <v>-4.246714684800005</v>
       </c>
       <c r="P73">
-        <v>-9.18220925160001</v>
+        <v>-9.909000931200012</v>
       </c>
       <c r="Q73">
-        <v>-5.882209251600013</v>
+        <v>-6.609000931200015</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2097135423032718</v>
+        <v>0.2155675973855316</v>
       </c>
       <c r="T73">
-        <v>1.585169230307349</v>
+        <v>1.64178241710404</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2466173480664572</v>
+        <v>0.2431921071210898</v>
       </c>
       <c r="W73">
-        <v>0.1105965733038441</v>
+        <v>0.111099398674624</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8220578268881908</v>
+        <v>0.8106403570702992</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1403504943136782</v>
+        <v>0.1834939495883089</v>
       </c>
       <c r="C74">
-        <v>-69.6601486973214</v>
+        <v>-207.6337141317686</v>
       </c>
       <c r="D74">
-        <v>417.7749713026786</v>
+        <v>286.8741158682315</v>
       </c>
       <c r="E74">
-        <v>509.16412</v>
+        <v>516.2368300000001</v>
       </c>
       <c r="F74">
-        <v>509.2351200000001</v>
+        <v>516.3078300000001</v>
       </c>
       <c r="G74">
         <v>21.8</v>
@@ -7355,45 +7355,45 @@
         <v>60.6</v>
       </c>
       <c r="M74">
-        <v>74.75571561600002</v>
+        <v>103.674612264</v>
       </c>
       <c r="N74">
-        <v>-14.15571561600002</v>
+        <v>-43.07461226400002</v>
       </c>
       <c r="O74">
-        <v>-4.246714684800005</v>
+        <v>-12.9223836792</v>
       </c>
       <c r="P74">
-        <v>-9.909000931200012</v>
+        <v>-30.15222858480001</v>
       </c>
       <c r="Q74">
-        <v>-6.609000931200015</v>
+        <v>-26.85222858480002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2155675973855316</v>
+        <v>0.2319051205280728</v>
       </c>
       <c r="T74">
-        <v>1.64178241710404</v>
+        <v>1.799778752373733</v>
       </c>
       <c r="U74">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.2431921071210898</v>
+        <v>0.1753563346222692</v>
       </c>
       <c r="W74">
-        <v>0.111099398674624</v>
+        <v>0.1655884480078484</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y74">
-        <v>0.8106403570702992</v>
+        <v>0.584521115407564</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1834939495883089</v>
+        <v>0.1850439495883089</v>
       </c>
       <c r="C75">
-        <v>-207.6337141317686</v>
+        <v>-217.8997756627357</v>
       </c>
       <c r="D75">
-        <v>286.8741158682315</v>
+        <v>283.6807643372642</v>
       </c>
       <c r="E75">
-        <v>516.2368300000001</v>
+        <v>523.30954</v>
       </c>
       <c r="F75">
-        <v>516.3078300000001</v>
+        <v>523.38054</v>
       </c>
       <c r="G75">
         <v>21.8</v>
@@ -7437,37 +7437,37 @@
         <v>60.6</v>
       </c>
       <c r="M75">
-        <v>103.674612264</v>
+        <v>105.094812432</v>
       </c>
       <c r="N75">
-        <v>-43.07461226400002</v>
+        <v>-44.494812432</v>
       </c>
       <c r="O75">
-        <v>-12.9223836792</v>
+        <v>-13.3484437296</v>
       </c>
       <c r="P75">
-        <v>-30.15222858480001</v>
+        <v>-31.1463687024</v>
       </c>
       <c r="Q75">
-        <v>-26.85222858480002</v>
+        <v>-27.8463687024</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2319051205280728</v>
+        <v>0.2390630097791525</v>
       </c>
       <c r="T75">
-        <v>1.799778752373733</v>
+        <v>1.869001012080414</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1753563346222692</v>
+        <v>0.172986654424671</v>
       </c>
       <c r="W75">
-        <v>0.1655884480078484</v>
+        <v>0.1660642797915261</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.584521115407564</v>
+        <v>0.57662218141557</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1850439495883089</v>
+        <v>0.1865939495883089</v>
       </c>
       <c r="C76">
-        <v>-217.8997756627357</v>
+        <v>-228.095526006504</v>
       </c>
       <c r="D76">
-        <v>283.6807643372642</v>
+        <v>280.557723993496</v>
       </c>
       <c r="E76">
-        <v>523.30954</v>
+        <v>530.38225</v>
       </c>
       <c r="F76">
-        <v>523.38054</v>
+        <v>530.45325</v>
       </c>
       <c r="G76">
         <v>21.8</v>
@@ -7519,37 +7519,37 @@
         <v>60.6</v>
       </c>
       <c r="M76">
-        <v>105.094812432</v>
+        <v>106.5150126</v>
       </c>
       <c r="N76">
-        <v>-44.494812432</v>
+        <v>-45.9150126</v>
       </c>
       <c r="O76">
-        <v>-13.3484437296</v>
+        <v>-13.77450378</v>
       </c>
       <c r="P76">
-        <v>-31.1463687024</v>
+        <v>-32.14050882</v>
       </c>
       <c r="Q76">
-        <v>-27.8463687024</v>
+        <v>-28.84050882</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2390630097791525</v>
+        <v>0.2467935301703186</v>
       </c>
       <c r="T76">
-        <v>1.869001012080414</v>
+        <v>1.943761052563631</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.172986654424671</v>
+        <v>0.1706801656990087</v>
       </c>
       <c r="W76">
-        <v>0.1660642797915261</v>
+        <v>0.1665274227276391</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.57662218141557</v>
+        <v>0.5689338856633623</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1865939495883089</v>
+        <v>0.188143949588309</v>
       </c>
       <c r="C77">
-        <v>-228.095526006504</v>
+        <v>-238.2232620434212</v>
       </c>
       <c r="D77">
-        <v>280.557723993496</v>
+        <v>277.5026979565788</v>
       </c>
       <c r="E77">
-        <v>530.38225</v>
+        <v>537.45496</v>
       </c>
       <c r="F77">
-        <v>530.45325</v>
+        <v>537.5259600000001</v>
       </c>
       <c r="G77">
         <v>21.8</v>
@@ -7601,37 +7601,37 @@
         <v>60.6</v>
       </c>
       <c r="M77">
-        <v>106.5150126</v>
+        <v>107.935212768</v>
       </c>
       <c r="N77">
-        <v>-45.9150126</v>
+        <v>-47.33521276800001</v>
       </c>
       <c r="O77">
-        <v>-13.77450378</v>
+        <v>-14.2005638304</v>
       </c>
       <c r="P77">
-        <v>-32.14050882</v>
+        <v>-33.13464893760001</v>
       </c>
       <c r="Q77">
-        <v>-28.84050882</v>
+        <v>-29.83464893760001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2467935301703186</v>
+        <v>0.2551682605940819</v>
       </c>
       <c r="T77">
-        <v>1.943761052563631</v>
+        <v>2.02475109642045</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.1706801656990087</v>
+        <v>0.1684343740450744</v>
       </c>
       <c r="W77">
-        <v>0.1665274227276391</v>
+        <v>0.1669783776917491</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5689338856633623</v>
+        <v>0.5614479134835813</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.188143949588309</v>
+        <v>0.189693949588309</v>
       </c>
       <c r="C78">
-        <v>-238.2232620434212</v>
+        <v>-248.2851816874913</v>
       </c>
       <c r="D78">
-        <v>277.5026979565788</v>
+        <v>274.5134883125087</v>
       </c>
       <c r="E78">
-        <v>537.45496</v>
+        <v>544.5276700000001</v>
       </c>
       <c r="F78">
-        <v>537.5259600000001</v>
+        <v>544.5986700000001</v>
       </c>
       <c r="G78">
         <v>21.8</v>
@@ -7683,37 +7683,37 @@
         <v>60.6</v>
       </c>
       <c r="M78">
-        <v>107.935212768</v>
+        <v>109.355412936</v>
       </c>
       <c r="N78">
-        <v>-47.33521276800001</v>
+        <v>-48.75541293600002</v>
       </c>
       <c r="O78">
-        <v>-14.2005638304</v>
+        <v>-14.62662388080001</v>
       </c>
       <c r="P78">
-        <v>-33.13464893760001</v>
+        <v>-34.12878905520002</v>
       </c>
       <c r="Q78">
-        <v>-29.83464893760001</v>
+        <v>-30.82878905520002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2551682605940819</v>
+        <v>0.2642712284459985</v>
       </c>
       <c r="T78">
-        <v>2.02475109642045</v>
+        <v>2.112783752786556</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1684343740450744</v>
+        <v>0.1662469146418916</v>
       </c>
       <c r="W78">
-        <v>0.1669783776917491</v>
+        <v>0.1674176195399082</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5614479134835813</v>
+        <v>0.5541563821396386</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.189693949588309</v>
+        <v>0.191243949588309</v>
       </c>
       <c r="C79">
-        <v>-248.2851816874913</v>
+        <v>-258.2833891598083</v>
       </c>
       <c r="D79">
-        <v>274.5134883125087</v>
+        <v>271.5879908401918</v>
       </c>
       <c r="E79">
-        <v>544.5276700000001</v>
+        <v>551.6003800000001</v>
       </c>
       <c r="F79">
-        <v>544.5986700000001</v>
+        <v>551.6713800000001</v>
       </c>
       <c r="G79">
         <v>21.8</v>
@@ -7765,37 +7765,37 @@
         <v>60.6</v>
       </c>
       <c r="M79">
-        <v>109.355412936</v>
+        <v>110.775613104</v>
       </c>
       <c r="N79">
-        <v>-48.75541293600002</v>
+        <v>-50.17561310400003</v>
       </c>
       <c r="O79">
-        <v>-14.62662388080001</v>
+        <v>-15.05268393120001</v>
       </c>
       <c r="P79">
-        <v>-34.12878905520002</v>
+        <v>-35.12292917280002</v>
       </c>
       <c r="Q79">
-        <v>-30.82878905520002</v>
+        <v>-31.82292917280002</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2642712284459985</v>
+        <v>0.2742017388299076</v>
       </c>
       <c r="T79">
-        <v>2.112783752786556</v>
+        <v>2.208819377913218</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1662469146418916</v>
+        <v>0.1641155439413545</v>
       </c>
       <c r="W79">
-        <v>0.1674176195399082</v>
+        <v>0.167845598776576</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5541563821396386</v>
+        <v>0.5470518131378483</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.191243949588309</v>
+        <v>0.1927939495883089</v>
       </c>
       <c r="C80">
-        <v>-258.2833891598083</v>
+        <v>-268.219899928352</v>
       </c>
       <c r="D80">
-        <v>271.5879908401918</v>
+        <v>268.724190071648</v>
       </c>
       <c r="E80">
-        <v>551.6003800000001</v>
+        <v>558.67309</v>
       </c>
       <c r="F80">
-        <v>551.6713800000001</v>
+        <v>558.74409</v>
       </c>
       <c r="G80">
         <v>21.8</v>
@@ -7847,37 +7847,37 @@
         <v>60.6</v>
       </c>
       <c r="M80">
-        <v>110.775613104</v>
+        <v>112.195813272</v>
       </c>
       <c r="N80">
-        <v>-50.17561310400003</v>
+        <v>-51.59581327200001</v>
       </c>
       <c r="O80">
-        <v>-15.05268393120001</v>
+        <v>-15.4787439816</v>
       </c>
       <c r="P80">
-        <v>-35.12292917280002</v>
+        <v>-36.11706929040001</v>
       </c>
       <c r="Q80">
-        <v>-31.82292917280002</v>
+        <v>-32.81706929040001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2742017388299076</v>
+        <v>0.2850780121075222</v>
       </c>
       <c r="T80">
-        <v>2.208819377913218</v>
+        <v>2.314001253051942</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1641155439413545</v>
+        <v>0.1620381319927298</v>
       </c>
       <c r="W80">
-        <v>0.167845598776576</v>
+        <v>0.1682627430958599</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5470518131378483</v>
+        <v>0.5401271066424326</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1927939495883089</v>
+        <v>0.194343949588309</v>
       </c>
       <c r="C81">
-        <v>-268.219899928352</v>
+        <v>-278.0966453385149</v>
       </c>
       <c r="D81">
-        <v>268.724190071648</v>
+        <v>265.9201546614851</v>
       </c>
       <c r="E81">
-        <v>558.67309</v>
+        <v>565.7458</v>
       </c>
       <c r="F81">
-        <v>558.74409</v>
+        <v>565.8168000000001</v>
       </c>
       <c r="G81">
         <v>21.8</v>
@@ -7929,37 +7929,37 @@
         <v>60.6</v>
       </c>
       <c r="M81">
-        <v>112.195813272</v>
+        <v>113.61601344</v>
       </c>
       <c r="N81">
-        <v>-51.59581327200001</v>
+        <v>-53.01601344000002</v>
       </c>
       <c r="O81">
-        <v>-15.4787439816</v>
+        <v>-15.904804032</v>
       </c>
       <c r="P81">
-        <v>-36.11706929040001</v>
+        <v>-37.11120940800001</v>
       </c>
       <c r="Q81">
-        <v>-32.81706929040001</v>
+        <v>-33.81120940800001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2850780121075222</v>
+        <v>0.2970419127128983</v>
       </c>
       <c r="T81">
-        <v>2.314001253051942</v>
+        <v>2.429701315704539</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1620381319927298</v>
+        <v>0.1600126553428206</v>
       </c>
       <c r="W81">
-        <v>0.1682627430958599</v>
+        <v>0.1686694588071616</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5401271066424326</v>
+        <v>0.5333755178094022</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.194343949588309</v>
+        <v>0.195893949588309</v>
       </c>
       <c r="C82">
-        <v>-278.0966453385149</v>
+        <v>-287.9154769567138</v>
       </c>
       <c r="D82">
-        <v>265.9201546614851</v>
+        <v>263.1740330432863</v>
       </c>
       <c r="E82">
-        <v>565.7458</v>
+        <v>572.8185100000001</v>
       </c>
       <c r="F82">
-        <v>565.8168000000001</v>
+        <v>572.8895100000001</v>
       </c>
       <c r="G82">
         <v>21.8</v>
@@ -8011,37 +8011,37 @@
         <v>60.6</v>
       </c>
       <c r="M82">
-        <v>113.61601344</v>
+        <v>115.036213608</v>
       </c>
       <c r="N82">
-        <v>-53.01601344000002</v>
+        <v>-54.43621360800002</v>
       </c>
       <c r="O82">
-        <v>-15.904804032</v>
+        <v>-16.33086408240001</v>
       </c>
       <c r="P82">
-        <v>-37.11120940800001</v>
+        <v>-38.10534952560002</v>
       </c>
       <c r="Q82">
-        <v>-33.81120940800001</v>
+        <v>-34.80534952560002</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2970419127128983</v>
+        <v>0.3102651712767351</v>
       </c>
       <c r="T82">
-        <v>2.429701315704539</v>
+        <v>2.557580332320568</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1600126553428206</v>
+        <v>0.1580371904620451</v>
       </c>
       <c r="W82">
-        <v>0.1686694588071616</v>
+        <v>0.1690661321552214</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5333755178094022</v>
+        <v>0.5267906348734835</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.195893949588309</v>
+        <v>0.197443949588309</v>
       </c>
       <c r="C83">
-        <v>-287.9154769567138</v>
+        <v>-297.6781706476196</v>
       </c>
       <c r="D83">
-        <v>263.1740330432863</v>
+        <v>260.4840493523805</v>
       </c>
       <c r="E83">
-        <v>572.8185100000001</v>
+        <v>579.8912200000001</v>
       </c>
       <c r="F83">
-        <v>572.8895100000001</v>
+        <v>579.9622200000001</v>
       </c>
       <c r="G83">
         <v>21.8</v>
@@ -8093,37 +8093,37 @@
         <v>60.6</v>
       </c>
       <c r="M83">
-        <v>115.036213608</v>
+        <v>116.456413776</v>
       </c>
       <c r="N83">
-        <v>-54.43621360800002</v>
+        <v>-55.85641377600003</v>
       </c>
       <c r="O83">
-        <v>-16.33086408240001</v>
+        <v>-16.75692413280001</v>
       </c>
       <c r="P83">
-        <v>-38.10534952560002</v>
+        <v>-39.09948964320002</v>
       </c>
       <c r="Q83">
-        <v>-34.80534952560002</v>
+        <v>-35.79948964320003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3102651712767351</v>
+        <v>0.3249576807921093</v>
       </c>
       <c r="T83">
-        <v>2.557580332320568</v>
+        <v>2.699668128560599</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1580371904620451</v>
+        <v>0.1561099076515323</v>
       </c>
       <c r="W83">
-        <v>0.1690661321552214</v>
+        <v>0.1694531305435723</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5267906348734835</v>
+        <v>0.5203663588384411</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.197443949588309</v>
+        <v>0.1989939495883089</v>
       </c>
       <c r="C84">
-        <v>-297.6781706476196</v>
+        <v>-307.3864304038679</v>
       </c>
       <c r="D84">
-        <v>260.4840493523805</v>
+        <v>257.8484995961322</v>
       </c>
       <c r="E84">
-        <v>579.8912200000001</v>
+        <v>586.9639300000001</v>
       </c>
       <c r="F84">
-        <v>579.9622200000001</v>
+        <v>587.0349300000001</v>
       </c>
       <c r="G84">
         <v>21.8</v>
@@ -8175,37 +8175,37 @@
         <v>60.6</v>
       </c>
       <c r="M84">
-        <v>116.456413776</v>
+        <v>117.876613944</v>
       </c>
       <c r="N84">
-        <v>-55.85641377600003</v>
+        <v>-57.27661394400003</v>
       </c>
       <c r="O84">
-        <v>-16.75692413280001</v>
+        <v>-17.18298418320001</v>
       </c>
       <c r="P84">
-        <v>-39.09948964320002</v>
+        <v>-40.09362976080002</v>
       </c>
       <c r="Q84">
-        <v>-35.79948964320003</v>
+        <v>-36.79362976080002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3249576807921093</v>
+        <v>0.341378720838704</v>
       </c>
       <c r="T84">
-        <v>2.699668128560599</v>
+        <v>2.858472136122988</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1561099076515323</v>
+        <v>0.1542290653906705</v>
       </c>
       <c r="W84">
-        <v>0.1694531305435723</v>
+        <v>0.1698308036695534</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5203663588384411</v>
+        <v>0.5140968846355682</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1989939495883089</v>
+        <v>0.200543949588309</v>
       </c>
       <c r="C85">
-        <v>-307.3864304038679</v>
+        <v>-317.0418919456071</v>
       </c>
       <c r="D85">
-        <v>257.8484995961322</v>
+        <v>255.265748054393</v>
       </c>
       <c r="E85">
-        <v>586.9639300000001</v>
+        <v>594.03664</v>
       </c>
       <c r="F85">
-        <v>587.0349300000001</v>
+        <v>594.1076400000001</v>
       </c>
       <c r="G85">
         <v>21.8</v>
@@ -8257,37 +8257,37 @@
         <v>60.6</v>
       </c>
       <c r="M85">
-        <v>117.876613944</v>
+        <v>119.296814112</v>
       </c>
       <c r="N85">
-        <v>-57.27661394400003</v>
+        <v>-58.69681411200002</v>
       </c>
       <c r="O85">
-        <v>-17.18298418320001</v>
+        <v>-17.60904423360001</v>
       </c>
       <c r="P85">
-        <v>-40.09362976080002</v>
+        <v>-41.08776987840001</v>
       </c>
       <c r="Q85">
-        <v>-36.79362976080002</v>
+        <v>-37.78776987840001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.341378720838704</v>
+        <v>0.359852390891123</v>
       </c>
       <c r="T85">
-        <v>2.858472136122988</v>
+        <v>3.037126644630675</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1542290653906705</v>
+        <v>0.1523930050884006</v>
       </c>
       <c r="W85">
-        <v>0.1698308036695534</v>
+        <v>0.1701994845782492</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5140968846355682</v>
+        <v>0.507976683628002</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2005439495883089</v>
+        <v>0.202093949588309</v>
       </c>
       <c r="C86">
-        <v>-317.0418919456069</v>
+        <v>-326.646126105861</v>
       </c>
       <c r="D86">
-        <v>255.2657480543931</v>
+        <v>252.7342238941391</v>
       </c>
       <c r="E86">
-        <v>594.03664</v>
+        <v>601.1093500000001</v>
       </c>
       <c r="F86">
-        <v>594.1076400000001</v>
+        <v>601.1803500000001</v>
       </c>
       <c r="G86">
         <v>21.8</v>
@@ -8339,37 +8339,37 @@
         <v>60.6</v>
       </c>
       <c r="M86">
-        <v>119.296814112</v>
+        <v>120.71701428</v>
       </c>
       <c r="N86">
-        <v>-58.69681411200002</v>
+        <v>-60.11701428000001</v>
       </c>
       <c r="O86">
-        <v>-17.60904423360001</v>
+        <v>-18.035104284</v>
       </c>
       <c r="P86">
-        <v>-41.08776987840001</v>
+        <v>-42.08190999600001</v>
       </c>
       <c r="Q86">
-        <v>-37.78776987840001</v>
+        <v>-38.78190999600001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3598523908911228</v>
+        <v>0.380789216950531</v>
       </c>
       <c r="T86">
-        <v>3.037126644630673</v>
+        <v>3.239601754272718</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1523930050884006</v>
+        <v>0.1506001462050077</v>
       </c>
       <c r="W86">
-        <v>0.1701994845782492</v>
+        <v>0.1705594906420345</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.507976683628002</v>
+        <v>0.5020004873500256</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.202093949588309</v>
+        <v>0.2348388615665276</v>
       </c>
       <c r="C87">
-        <v>-326.646126105861</v>
+        <v>-377.4969240964326</v>
       </c>
       <c r="D87">
-        <v>252.7342238941391</v>
+        <v>208.9561359035673</v>
       </c>
       <c r="E87">
-        <v>601.1093500000001</v>
+        <v>608.18206</v>
       </c>
       <c r="F87">
-        <v>601.1803500000001</v>
+        <v>608.25306</v>
       </c>
       <c r="G87">
         <v>21.8</v>
@@ -8421,45 +8421,45 @@
         <v>60.6</v>
       </c>
       <c r="M87">
-        <v>120.71701428</v>
+        <v>143.426071548</v>
       </c>
       <c r="N87">
-        <v>-60.11701428000001</v>
+        <v>-82.82607154800002</v>
       </c>
       <c r="O87">
-        <v>-18.035104284</v>
+        <v>-24.8478214644</v>
       </c>
       <c r="P87">
-        <v>-42.08190999600001</v>
+        <v>-57.97825008360002</v>
       </c>
       <c r="Q87">
-        <v>-38.78190999600001</v>
+        <v>-54.67825008360002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.380789216950531</v>
+        <v>0.4125378180057018</v>
       </c>
       <c r="T87">
-        <v>3.239601754272718</v>
+        <v>3.546634991373077</v>
       </c>
       <c r="U87">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1506001462050077</v>
+        <v>0.126755197320703</v>
       </c>
       <c r="W87">
-        <v>0.1705594906420345</v>
+        <v>0.2059111244717783</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y87">
-        <v>0.5020004873500256</v>
+        <v>0.4225173244023431</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2348388615665276</v>
+        <v>0.2367388615665276</v>
       </c>
       <c r="C88">
-        <v>-377.4969240964326</v>
+        <v>-386.6489209160959</v>
       </c>
       <c r="D88">
-        <v>208.9561359035673</v>
+        <v>206.8768490839041</v>
       </c>
       <c r="E88">
-        <v>608.18206</v>
+        <v>615.25477</v>
       </c>
       <c r="F88">
-        <v>608.25306</v>
+        <v>615.32577</v>
       </c>
       <c r="G88">
         <v>21.8</v>
@@ -8503,37 +8503,37 @@
         <v>60.6</v>
       </c>
       <c r="M88">
-        <v>143.426071548</v>
+        <v>145.093816566</v>
       </c>
       <c r="N88">
-        <v>-82.82607154800002</v>
+        <v>-84.49381656600002</v>
       </c>
       <c r="O88">
-        <v>-24.8478214644</v>
+        <v>-25.34814496980001</v>
       </c>
       <c r="P88">
-        <v>-57.97825008360002</v>
+        <v>-59.14567159620002</v>
       </c>
       <c r="Q88">
-        <v>-54.67825008360002</v>
+        <v>-55.84567159620002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4125378180057018</v>
+        <v>0.4407484193907559</v>
       </c>
       <c r="T88">
-        <v>3.546634991373077</v>
+        <v>3.819453067632546</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.126755197320703</v>
+        <v>0.1252982410296604</v>
       </c>
       <c r="W88">
-        <v>0.2059111244717783</v>
+        <v>0.2062546747652061</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4225173244023431</v>
+        <v>0.4176608034322012</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2367388615665276</v>
+        <v>0.2386388615665276</v>
       </c>
       <c r="C89">
-        <v>-386.6489209160959</v>
+        <v>-395.7599442003913</v>
       </c>
       <c r="D89">
-        <v>206.8768490839041</v>
+        <v>204.8385357996088</v>
       </c>
       <c r="E89">
-        <v>615.25477</v>
+        <v>622.32748</v>
       </c>
       <c r="F89">
-        <v>615.32577</v>
+        <v>622.3984800000001</v>
       </c>
       <c r="G89">
         <v>21.8</v>
@@ -8585,37 +8585,37 @@
         <v>60.6</v>
       </c>
       <c r="M89">
-        <v>145.093816566</v>
+        <v>146.761561584</v>
       </c>
       <c r="N89">
-        <v>-84.49381656600002</v>
+        <v>-86.16156158400003</v>
       </c>
       <c r="O89">
-        <v>-25.34814496980001</v>
+        <v>-25.84846847520001</v>
       </c>
       <c r="P89">
-        <v>-59.14567159620002</v>
+        <v>-60.31309310880002</v>
       </c>
       <c r="Q89">
-        <v>-55.84567159620002</v>
+        <v>-57.01309310880002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4407484193907559</v>
+        <v>0.4736607876733189</v>
       </c>
       <c r="T89">
-        <v>3.819453067632546</v>
+        <v>4.137740823268592</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1252982410296604</v>
+        <v>0.123874397381596</v>
       </c>
       <c r="W89">
-        <v>0.2062546747652061</v>
+        <v>0.2065904170974197</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4176608034322012</v>
+        <v>0.4129146579386535</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2386388615665276</v>
+        <v>0.2405388615665276</v>
       </c>
       <c r="C90">
-        <v>-395.7599442003913</v>
+        <v>-404.8311932433357</v>
       </c>
       <c r="D90">
-        <v>204.8385357996088</v>
+        <v>202.8399967566644</v>
       </c>
       <c r="E90">
-        <v>622.32748</v>
+        <v>629.4001900000001</v>
       </c>
       <c r="F90">
-        <v>622.3984800000001</v>
+        <v>629.4711900000001</v>
       </c>
       <c r="G90">
         <v>21.8</v>
@@ -8667,37 +8667,37 @@
         <v>60.6</v>
       </c>
       <c r="M90">
-        <v>146.761561584</v>
+        <v>148.429306602</v>
       </c>
       <c r="N90">
-        <v>-86.16156158400003</v>
+        <v>-87.82930660200003</v>
       </c>
       <c r="O90">
-        <v>-25.84846847520001</v>
+        <v>-26.34879198060001</v>
       </c>
       <c r="P90">
-        <v>-60.31309310880002</v>
+        <v>-61.48051462140002</v>
       </c>
       <c r="Q90">
-        <v>-57.01309310880002</v>
+        <v>-58.18051462140002</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4736607876733189</v>
+        <v>0.5125572229163479</v>
       </c>
       <c r="T90">
-        <v>4.137740823268592</v>
+        <v>4.513899079929373</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.123874397381596</v>
+        <v>0.1224825502200051</v>
       </c>
       <c r="W90">
-        <v>0.2065904170974197</v>
+        <v>0.2069186146581228</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4129146579386535</v>
+        <v>0.4082751674000169</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2405388615665276</v>
+        <v>0.2424388615665276</v>
       </c>
       <c r="C91">
-        <v>-404.8311932433357</v>
+        <v>-413.8638209867938</v>
       </c>
       <c r="D91">
-        <v>202.8399967566644</v>
+        <v>200.8800790132063</v>
       </c>
       <c r="E91">
-        <v>629.4001900000001</v>
+        <v>636.4729000000001</v>
       </c>
       <c r="F91">
-        <v>629.4711900000001</v>
+        <v>636.5439000000001</v>
       </c>
       <c r="G91">
         <v>21.8</v>
@@ -8749,37 +8749,37 @@
         <v>60.6</v>
       </c>
       <c r="M91">
-        <v>148.429306602</v>
+        <v>150.09705162</v>
       </c>
       <c r="N91">
-        <v>-87.82930660200003</v>
+        <v>-89.49705162000004</v>
       </c>
       <c r="O91">
-        <v>-26.34879198060001</v>
+        <v>-26.84911548600001</v>
       </c>
       <c r="P91">
-        <v>-61.48051462140002</v>
+        <v>-62.64793613400003</v>
       </c>
       <c r="Q91">
-        <v>-58.18051462140002</v>
+        <v>-59.34793613400003</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5125572229163479</v>
+        <v>0.5592329452079827</v>
       </c>
       <c r="T91">
-        <v>4.513899079929373</v>
+        <v>4.96528898792231</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1224825502200051</v>
+        <v>0.1211216329953383</v>
       </c>
       <c r="W91">
-        <v>0.2069186146581228</v>
+        <v>0.2072395189396992</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4082751674000169</v>
+        <v>0.4037387766511278</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2424388615665276</v>
+        <v>0.2443388615665276</v>
       </c>
       <c r="C92">
-        <v>-413.8638209867938</v>
+        <v>-422.8589362384084</v>
       </c>
       <c r="D92">
-        <v>200.8800790132063</v>
+        <v>198.9576737615916</v>
       </c>
       <c r="E92">
-        <v>636.4729000000001</v>
+        <v>643.54561</v>
       </c>
       <c r="F92">
-        <v>636.5439000000001</v>
+        <v>643.61661</v>
       </c>
       <c r="G92">
         <v>21.8</v>
@@ -8831,37 +8831,37 @@
         <v>60.6</v>
       </c>
       <c r="M92">
-        <v>150.09705162</v>
+        <v>151.764796638</v>
       </c>
       <c r="N92">
-        <v>-89.49705162000004</v>
+        <v>-91.16479663800001</v>
       </c>
       <c r="O92">
-        <v>-26.84911548600001</v>
+        <v>-27.3494389914</v>
       </c>
       <c r="P92">
-        <v>-62.64793613400003</v>
+        <v>-63.81535764660001</v>
       </c>
       <c r="Q92">
-        <v>-59.34793613400003</v>
+        <v>-60.51535764660001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5592329452079827</v>
+        <v>0.6162810502310919</v>
       </c>
       <c r="T92">
-        <v>4.96528898792231</v>
+        <v>5.516987764358123</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1211216329953383</v>
+        <v>0.1197906260393456</v>
       </c>
       <c r="W92">
-        <v>0.2072395189396992</v>
+        <v>0.2075533703799223</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4037387766511278</v>
+        <v>0.3993020867978188</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2443388615665276</v>
+        <v>0.2462388615665276</v>
       </c>
       <c r="C93">
-        <v>-422.8589362384084</v>
+        <v>-431.8176057633859</v>
       </c>
       <c r="D93">
-        <v>198.9576737615916</v>
+        <v>197.0717142366142</v>
       </c>
       <c r="E93">
-        <v>643.54561</v>
+        <v>650.61832</v>
       </c>
       <c r="F93">
-        <v>643.61661</v>
+        <v>650.6893200000001</v>
       </c>
       <c r="G93">
         <v>21.8</v>
@@ -8913,37 +8913,37 @@
         <v>60.6</v>
       </c>
       <c r="M93">
-        <v>151.764796638</v>
+        <v>153.432541656</v>
       </c>
       <c r="N93">
-        <v>-91.16479663800001</v>
+        <v>-92.83254165600002</v>
       </c>
       <c r="O93">
-        <v>-27.3494389914</v>
+        <v>-27.8497624968</v>
       </c>
       <c r="P93">
-        <v>-63.81535764660001</v>
+        <v>-64.98277915920002</v>
       </c>
       <c r="Q93">
-        <v>-60.51535764660001</v>
+        <v>-61.68277915920002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6162810502310919</v>
+        <v>0.6875911815099787</v>
       </c>
       <c r="T93">
-        <v>5.516987764358123</v>
+        <v>6.206611234902891</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.1197906260393456</v>
+        <v>0.1184885540171788</v>
       </c>
       <c r="W93">
-        <v>0.2075533703799223</v>
+        <v>0.2078603989627492</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3993020867978188</v>
+        <v>0.3949618467239294</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2462388615665276</v>
+        <v>0.2481388615665276</v>
       </c>
       <c r="C94">
-        <v>-431.8176057633859</v>
+        <v>-440.740856258428</v>
       </c>
       <c r="D94">
-        <v>197.0717142366142</v>
+        <v>195.221173741572</v>
       </c>
       <c r="E94">
-        <v>650.61832</v>
+        <v>657.6910300000001</v>
       </c>
       <c r="F94">
-        <v>650.6893200000001</v>
+        <v>657.7620300000001</v>
       </c>
       <c r="G94">
         <v>21.8</v>
@@ -8995,37 +8995,37 @@
         <v>60.6</v>
       </c>
       <c r="M94">
-        <v>153.432541656</v>
+        <v>155.100286674</v>
       </c>
       <c r="N94">
-        <v>-92.83254165600002</v>
+        <v>-94.50028667400002</v>
       </c>
       <c r="O94">
-        <v>-27.8497624968</v>
+        <v>-28.3500860022</v>
       </c>
       <c r="P94">
-        <v>-64.98277915920002</v>
+        <v>-66.15020067180002</v>
       </c>
       <c r="Q94">
-        <v>-61.68277915920002</v>
+        <v>-62.85020067180002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6875911815099787</v>
+        <v>0.7792756360114043</v>
       </c>
       <c r="T94">
-        <v>6.206611234902891</v>
+        <v>7.093269982746161</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1184885540171788</v>
+        <v>0.1172144835438758</v>
       </c>
       <c r="W94">
-        <v>0.2078603989627492</v>
+        <v>0.2081608247803541</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3949618467239294</v>
+        <v>0.3907149451462527</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2481388615665276</v>
+        <v>0.2500388615665275</v>
       </c>
       <c r="C95">
-        <v>-440.740856258428</v>
+        <v>-449.6296762154851</v>
       </c>
       <c r="D95">
-        <v>195.221173741572</v>
+        <v>193.405063784515</v>
       </c>
       <c r="E95">
-        <v>657.6910300000001</v>
+        <v>664.7637400000001</v>
       </c>
       <c r="F95">
-        <v>657.7620300000001</v>
+        <v>664.8347400000001</v>
       </c>
       <c r="G95">
         <v>21.8</v>
@@ -9077,37 +9077,37 @@
         <v>60.6</v>
       </c>
       <c r="M95">
-        <v>155.100286674</v>
+        <v>156.768031692</v>
       </c>
       <c r="N95">
-        <v>-94.50028667400002</v>
+        <v>-96.16803169200003</v>
       </c>
       <c r="O95">
-        <v>-28.3500860022</v>
+        <v>-28.85040950760001</v>
       </c>
       <c r="P95">
-        <v>-66.15020067180002</v>
+        <v>-67.31762218440002</v>
       </c>
       <c r="Q95">
-        <v>-62.85020067180002</v>
+        <v>-64.01762218440003</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7792756360114043</v>
+        <v>0.9015215753466383</v>
       </c>
       <c r="T95">
-        <v>7.093269982746161</v>
+        <v>8.275481646537189</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1172144835438758</v>
+        <v>0.1159675209529835</v>
       </c>
       <c r="W95">
-        <v>0.2081608247803541</v>
+        <v>0.2084548585592865</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3907149451462527</v>
+        <v>0.3865584031766117</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2500388615665275</v>
+        <v>0.2519388615665276</v>
       </c>
       <c r="C96">
-        <v>-449.6296762154851</v>
+        <v>-458.4850176824393</v>
       </c>
       <c r="D96">
-        <v>193.405063784515</v>
+        <v>191.6224323175609</v>
       </c>
       <c r="E96">
-        <v>664.7637400000001</v>
+        <v>671.8364500000001</v>
       </c>
       <c r="F96">
-        <v>664.8347400000001</v>
+        <v>671.9074500000002</v>
       </c>
       <c r="G96">
         <v>21.8</v>
@@ -9159,37 +9159,37 @@
         <v>60.6</v>
       </c>
       <c r="M96">
-        <v>156.768031692</v>
+        <v>158.4357767100001</v>
       </c>
       <c r="N96">
-        <v>-96.16803169200003</v>
+        <v>-97.83577671000006</v>
       </c>
       <c r="O96">
-        <v>-28.85040950760001</v>
+        <v>-29.35073301300002</v>
       </c>
       <c r="P96">
-        <v>-67.31762218440002</v>
+        <v>-68.48504369700004</v>
       </c>
       <c r="Q96">
-        <v>-64.01762218440003</v>
+        <v>-65.18504369700004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9015215753466383</v>
+        <v>1.072665890415967</v>
       </c>
       <c r="T96">
-        <v>8.275481646537189</v>
+        <v>9.930577975844633</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1159675209529835</v>
+        <v>0.11474681020611</v>
       </c>
       <c r="W96">
-        <v>0.2084548585592865</v>
+        <v>0.2087427021533993</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3865584031766117</v>
+        <v>0.3824893673537</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2519388615665276</v>
+        <v>0.2538388615665276</v>
       </c>
       <c r="C97">
-        <v>-458.4850176824393</v>
+        <v>-467.3077979273052</v>
       </c>
       <c r="D97">
-        <v>191.6224323175609</v>
+        <v>189.8723620726949</v>
       </c>
       <c r="E97">
-        <v>671.8364500000001</v>
+        <v>678.90916</v>
       </c>
       <c r="F97">
-        <v>671.9074500000002</v>
+        <v>678.9801600000001</v>
       </c>
       <c r="G97">
         <v>21.8</v>
@@ -9241,37 +9241,37 @@
         <v>60.6</v>
       </c>
       <c r="M97">
-        <v>158.4357767100001</v>
+        <v>160.103521728</v>
       </c>
       <c r="N97">
-        <v>-97.83577671000006</v>
+        <v>-99.50352172800004</v>
       </c>
       <c r="O97">
-        <v>-29.35073301300002</v>
+        <v>-29.85105651840001</v>
       </c>
       <c r="P97">
-        <v>-68.48504369700004</v>
+        <v>-69.65246520960002</v>
       </c>
       <c r="Q97">
-        <v>-65.18504369700004</v>
+        <v>-66.35246520960003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.072665890415967</v>
+        <v>1.329382363019959</v>
       </c>
       <c r="T97">
-        <v>9.930577975844633</v>
+        <v>12.4132224698058</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.11474681020611</v>
+        <v>0.1135515309331297</v>
       </c>
       <c r="W97">
-        <v>0.2087427021533993</v>
+        <v>0.209024549005968</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3824893673537</v>
+        <v>0.3785051031104323</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2538388615665276</v>
+        <v>0.2557388615665275</v>
       </c>
       <c r="C98">
-        <v>-467.3077979273052</v>
+        <v>-476.0989010120642</v>
       </c>
       <c r="D98">
-        <v>189.8723620726949</v>
+        <v>188.1539689879359</v>
       </c>
       <c r="E98">
-        <v>678.90916</v>
+        <v>685.9818700000001</v>
       </c>
       <c r="F98">
-        <v>678.9801600000001</v>
+        <v>686.0528700000001</v>
       </c>
       <c r="G98">
         <v>21.8</v>
@@ -9323,37 +9323,37 @@
         <v>60.6</v>
       </c>
       <c r="M98">
-        <v>160.103521728</v>
+        <v>161.771266746</v>
       </c>
       <c r="N98">
-        <v>-99.50352172800004</v>
+        <v>-101.171266746</v>
       </c>
       <c r="O98">
-        <v>-29.85105651840001</v>
+        <v>-30.35138002380001</v>
       </c>
       <c r="P98">
-        <v>-69.65246520960002</v>
+        <v>-70.81988672220004</v>
       </c>
       <c r="Q98">
-        <v>-66.35246520960003</v>
+        <v>-67.51988672220004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.329382363019956</v>
+        <v>1.757243150693274</v>
       </c>
       <c r="T98">
-        <v>12.41322246980576</v>
+        <v>16.55096329307435</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1135515309331297</v>
+        <v>0.1123808965936129</v>
       </c>
       <c r="W98">
-        <v>0.209024549005968</v>
+        <v>0.2093005845832261</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3785051031104323</v>
+        <v>0.3746029886453763</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2557388615665275</v>
+        <v>0.2576388615665275</v>
       </c>
       <c r="C99">
-        <v>-476.0989010120642</v>
+        <v>-484.8591792818021</v>
       </c>
       <c r="D99">
-        <v>188.1539689879359</v>
+        <v>186.4664007181979</v>
       </c>
       <c r="E99">
-        <v>685.9818700000001</v>
+        <v>693.05458</v>
       </c>
       <c r="F99">
-        <v>686.0528700000001</v>
+        <v>693.12558</v>
       </c>
       <c r="G99">
         <v>21.8</v>
@@ -9405,37 +9405,37 @@
         <v>60.6</v>
       </c>
       <c r="M99">
-        <v>161.771266746</v>
+        <v>163.439011764</v>
       </c>
       <c r="N99">
-        <v>-101.171266746</v>
+        <v>-102.839011764</v>
       </c>
       <c r="O99">
-        <v>-30.35138002380001</v>
+        <v>-30.85170352920001</v>
       </c>
       <c r="P99">
-        <v>-70.81988672220004</v>
+        <v>-71.98730823480001</v>
       </c>
       <c r="Q99">
-        <v>-67.51988672220004</v>
+        <v>-68.68730823480001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.757243150693274</v>
+        <v>2.612964726039911</v>
       </c>
       <c r="T99">
-        <v>16.55096329307435</v>
+        <v>24.82644493961153</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1123808965936129</v>
+        <v>0.1112341527508209</v>
       </c>
       <c r="W99">
-        <v>0.2093005845832261</v>
+        <v>0.2095709867813564</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3746029886453763</v>
+        <v>0.3707805091694031</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2576388615665275</v>
+        <v>0.2595388615665276</v>
       </c>
       <c r="C100">
-        <v>-484.8591792818021</v>
+        <v>-493.5894547744222</v>
       </c>
       <c r="D100">
-        <v>186.4664007181979</v>
+        <v>184.8088352255778</v>
       </c>
       <c r="E100">
-        <v>693.05458</v>
+        <v>700.12729</v>
       </c>
       <c r="F100">
-        <v>693.12558</v>
+        <v>700.19829</v>
       </c>
       <c r="G100">
         <v>21.8</v>
@@ -9487,37 +9487,37 @@
         <v>60.6</v>
       </c>
       <c r="M100">
-        <v>163.439011764</v>
+        <v>165.106756782</v>
       </c>
       <c r="N100">
-        <v>-102.839011764</v>
+        <v>-104.506756782</v>
       </c>
       <c r="O100">
-        <v>-30.85170352920001</v>
+        <v>-31.35202703460001</v>
       </c>
       <c r="P100">
-        <v>-71.98730823480001</v>
+        <v>-73.15472974740001</v>
       </c>
       <c r="Q100">
-        <v>-68.68730823480001</v>
+        <v>-69.85472974740001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.612964726039911</v>
+        <v>5.180129452079822</v>
       </c>
       <c r="T100">
-        <v>24.82644493961153</v>
+        <v>49.65288987922305</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1112341527508209</v>
+        <v>0.1101105754503076</v>
       </c>
       <c r="W100">
-        <v>0.2095709867813564</v>
+        <v>0.2098359263088175</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3707805091694031</v>
+        <v>0.3670352515010253</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2595388615665276</v>
-      </c>
-      <c r="C101">
-        <v>-493.5894547744222</v>
-      </c>
-      <c r="D101">
-        <v>184.8088352255778</v>
-      </c>
-      <c r="E101">
-        <v>700.12729</v>
-      </c>
-      <c r="F101">
-        <v>700.19829</v>
-      </c>
-      <c r="G101">
-        <v>21.8</v>
-      </c>
-      <c r="H101">
-        <v>707.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>63.9</v>
-      </c>
-      <c r="K101">
-        <v>3.299999999999997</v>
-      </c>
-      <c r="L101">
-        <v>60.6</v>
-      </c>
-      <c r="M101">
-        <v>165.106756782</v>
-      </c>
-      <c r="N101">
-        <v>-104.506756782</v>
-      </c>
-      <c r="O101">
-        <v>-31.35202703460001</v>
-      </c>
-      <c r="P101">
-        <v>-73.15472974740001</v>
-      </c>
-      <c r="Q101">
-        <v>-69.85472974740001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.180129452079822</v>
-      </c>
-      <c r="T101">
-        <v>49.65288987922305</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1101105754503076</v>
-      </c>
-      <c r="W101">
-        <v>0.2098359263088175</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3670352515010253</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
